--- a/apostas/Bolao_Copa2026_TurimMFO_Renata Mello.xlsx
+++ b/apostas/Bolao_Copa2026_TurimMFO_Renata Mello.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmello\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbrandao\Projetos\bolao-copa-2026\apostas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9232E1BA-86EE-4F52-9698-65C2A5A5CF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B7E276-20CA-4FD2-9378-CDFA22F54DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regras" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6771" uniqueCount="1619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6771" uniqueCount="1618">
   <si>
     <t>COMO FUNCIONA</t>
   </si>
@@ -4900,9 +4900,6 @@
       </rPr>
       <t>Chave PIX: asa@turimbr.com</t>
     </r>
-  </si>
-  <si>
-    <t>Kylian Mbappe</t>
   </si>
   <si>
     <t>X</t>
@@ -6200,111 +6197,64 @@
     <xf numFmtId="0" fontId="48" fillId="52" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="45" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="46" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="44" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="47" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="50" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="46" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="51" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="48" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="42" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="55" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6327,63 +6277,110 @@
     <xf numFmtId="0" fontId="56" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="48" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="49" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="51" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="44" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="47" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="50" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="45" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6765,25 +6762,25 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="B1:E44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="102.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="56.1" customHeight="1">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="174" t="s">
         <v>1596</v>
       </c>
-      <c r="C1" s="145"/>
-    </row>
-    <row r="2" spans="2:3" ht="27.95" customHeight="1">
-      <c r="B2" s="146" t="s">
+      <c r="C1" s="147"/>
+    </row>
+    <row r="2" spans="2:3" ht="27.9" customHeight="1">
+      <c r="B2" s="175" t="s">
         <v>745</v>
       </c>
-      <c r="C2" s="145"/>
+      <c r="C2" s="147"/>
     </row>
     <row r="3" spans="2:3" ht="24" customHeight="1">
       <c r="B3" s="1" t="s">
@@ -6797,7 +6794,7 @@
       <c r="B4" s="3" t="s">
         <v>1592</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="176" t="s">
         <v>1611</v>
       </c>
     </row>
@@ -6805,25 +6802,25 @@
       <c r="B5" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="C5" s="147"/>
+      <c r="C5" s="176"/>
     </row>
     <row r="6" spans="2:3" ht="27.75" customHeight="1">
       <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="147"/>
+      <c r="C6" s="176"/>
     </row>
     <row r="7" spans="2:3" ht="42" customHeight="1">
       <c r="B7" s="3" t="s">
         <v>1594</v>
       </c>
-      <c r="C7" s="147"/>
+      <c r="C7" s="176"/>
     </row>
     <row r="8" spans="2:3" ht="42" customHeight="1">
       <c r="B8" s="124" t="s">
         <v>1615</v>
       </c>
-      <c r="C8" s="147"/>
+      <c r="C8" s="176"/>
     </row>
     <row r="9" spans="2:3" ht="6" customHeight="1"/>
     <row r="10" spans="2:3" ht="24" customHeight="1">
@@ -6907,7 +6904,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="25.5">
+    <row r="23" spans="2:3" ht="26.4">
       <c r="B23" s="3" t="s">
         <v>1601</v>
       </c>
@@ -6917,7 +6914,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="25.5">
+    <row r="25" spans="2:3" ht="26.4">
       <c r="B25" s="124" t="s">
         <v>1603</v>
       </c>
@@ -7049,602 +7046,602 @@
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:EO34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="145" width="4.140625" customWidth="1"/>
+    <col min="2" max="145" width="4.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:145" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="145"/>
-      <c r="Z1" s="145"/>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="145"/>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="145"/>
-      <c r="AG1" s="145"/>
-      <c r="AH1" s="145"/>
-      <c r="AI1" s="145"/>
-      <c r="AJ1" s="145"/>
-      <c r="AK1" s="145"/>
-      <c r="AL1" s="145"/>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="145"/>
-      <c r="AO1" s="145"/>
-      <c r="AP1" s="145"/>
-      <c r="AQ1" s="145"/>
-      <c r="AR1" s="145"/>
-      <c r="AS1" s="145"/>
-      <c r="AT1" s="145"/>
-      <c r="AU1" s="145"/>
-      <c r="AV1" s="145"/>
-      <c r="AW1" s="145"/>
-      <c r="AX1" s="145"/>
-      <c r="AY1" s="145"/>
-      <c r="AZ1" s="145"/>
-      <c r="BA1" s="145"/>
-      <c r="BB1" s="145"/>
-      <c r="BC1" s="145"/>
-      <c r="BD1" s="145"/>
-      <c r="BE1" s="145"/>
-      <c r="BF1" s="145"/>
-      <c r="BG1" s="145"/>
-      <c r="BH1" s="145"/>
-      <c r="BI1" s="145"/>
-      <c r="BJ1" s="145"/>
-      <c r="BK1" s="145"/>
-      <c r="BL1" s="145"/>
-      <c r="BM1" s="145"/>
-      <c r="BN1" s="145"/>
-      <c r="BO1" s="145"/>
-      <c r="BP1" s="145"/>
-      <c r="BQ1" s="145"/>
-      <c r="BR1" s="145"/>
-      <c r="BS1" s="145"/>
-      <c r="BT1" s="145"/>
-      <c r="BU1" s="145"/>
-      <c r="BV1" s="145"/>
-      <c r="BW1" s="145"/>
-      <c r="BX1" s="145"/>
-      <c r="BY1" s="145"/>
-      <c r="BZ1" s="145"/>
-      <c r="CA1" s="145"/>
-      <c r="CB1" s="145"/>
-      <c r="CC1" s="145"/>
-      <c r="CD1" s="145"/>
-      <c r="CE1" s="145"/>
-      <c r="CF1" s="145"/>
-      <c r="CG1" s="145"/>
-      <c r="CH1" s="145"/>
-      <c r="CI1" s="145"/>
-      <c r="CJ1" s="145"/>
-      <c r="CK1" s="145"/>
-      <c r="CL1" s="145"/>
-      <c r="CM1" s="145"/>
-      <c r="CN1" s="145"/>
-      <c r="CO1" s="145"/>
-      <c r="CP1" s="145"/>
-      <c r="CQ1" s="145"/>
-      <c r="CR1" s="145"/>
-      <c r="CS1" s="145"/>
-      <c r="CT1" s="145"/>
-      <c r="CU1" s="145"/>
-      <c r="CV1" s="145"/>
-      <c r="CW1" s="145"/>
-      <c r="CX1" s="145"/>
-      <c r="CY1" s="145"/>
-      <c r="CZ1" s="145"/>
-      <c r="DA1" s="145"/>
-      <c r="DB1" s="145"/>
-      <c r="DC1" s="145"/>
-      <c r="DD1" s="145"/>
-      <c r="DE1" s="145"/>
-      <c r="DF1" s="145"/>
-      <c r="DG1" s="145"/>
-      <c r="DH1" s="145"/>
-      <c r="DI1" s="145"/>
-      <c r="DJ1" s="145"/>
-      <c r="DK1" s="145"/>
-      <c r="DL1" s="145"/>
-      <c r="DM1" s="145"/>
-      <c r="DN1" s="145"/>
-      <c r="DO1" s="145"/>
-      <c r="DP1" s="145"/>
-      <c r="DQ1" s="145"/>
-      <c r="DR1" s="145"/>
-      <c r="DS1" s="145"/>
-      <c r="DT1" s="145"/>
-      <c r="DU1" s="145"/>
-      <c r="DV1" s="145"/>
-      <c r="DW1" s="145"/>
-      <c r="DX1" s="145"/>
-      <c r="DY1" s="145"/>
-      <c r="DZ1" s="145"/>
-      <c r="EA1" s="145"/>
-      <c r="EB1" s="145"/>
-      <c r="EC1" s="145"/>
-      <c r="ED1" s="145"/>
-      <c r="EE1" s="145"/>
-      <c r="EF1" s="145"/>
-      <c r="EG1" s="145"/>
-      <c r="EH1" s="145"/>
-      <c r="EI1" s="145"/>
-      <c r="EJ1" s="145"/>
-      <c r="EK1" s="145"/>
-      <c r="EL1" s="145"/>
-      <c r="EM1" s="145"/>
-      <c r="EN1" s="145"/>
-      <c r="EO1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="147"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="147"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="147"/>
+      <c r="AJ1" s="147"/>
+      <c r="AK1" s="147"/>
+      <c r="AL1" s="147"/>
+      <c r="AM1" s="147"/>
+      <c r="AN1" s="147"/>
+      <c r="AO1" s="147"/>
+      <c r="AP1" s="147"/>
+      <c r="AQ1" s="147"/>
+      <c r="AR1" s="147"/>
+      <c r="AS1" s="147"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="147"/>
+      <c r="BA1" s="147"/>
+      <c r="BB1" s="147"/>
+      <c r="BC1" s="147"/>
+      <c r="BD1" s="147"/>
+      <c r="BE1" s="147"/>
+      <c r="BF1" s="147"/>
+      <c r="BG1" s="147"/>
+      <c r="BH1" s="147"/>
+      <c r="BI1" s="147"/>
+      <c r="BJ1" s="147"/>
+      <c r="BK1" s="147"/>
+      <c r="BL1" s="147"/>
+      <c r="BM1" s="147"/>
+      <c r="BN1" s="147"/>
+      <c r="BO1" s="147"/>
+      <c r="BP1" s="147"/>
+      <c r="BQ1" s="147"/>
+      <c r="BR1" s="147"/>
+      <c r="BS1" s="147"/>
+      <c r="BT1" s="147"/>
+      <c r="BU1" s="147"/>
+      <c r="BV1" s="147"/>
+      <c r="BW1" s="147"/>
+      <c r="BX1" s="147"/>
+      <c r="BY1" s="147"/>
+      <c r="BZ1" s="147"/>
+      <c r="CA1" s="147"/>
+      <c r="CB1" s="147"/>
+      <c r="CC1" s="147"/>
+      <c r="CD1" s="147"/>
+      <c r="CE1" s="147"/>
+      <c r="CF1" s="147"/>
+      <c r="CG1" s="147"/>
+      <c r="CH1" s="147"/>
+      <c r="CI1" s="147"/>
+      <c r="CJ1" s="147"/>
+      <c r="CK1" s="147"/>
+      <c r="CL1" s="147"/>
+      <c r="CM1" s="147"/>
+      <c r="CN1" s="147"/>
+      <c r="CO1" s="147"/>
+      <c r="CP1" s="147"/>
+      <c r="CQ1" s="147"/>
+      <c r="CR1" s="147"/>
+      <c r="CS1" s="147"/>
+      <c r="CT1" s="147"/>
+      <c r="CU1" s="147"/>
+      <c r="CV1" s="147"/>
+      <c r="CW1" s="147"/>
+      <c r="CX1" s="147"/>
+      <c r="CY1" s="147"/>
+      <c r="CZ1" s="147"/>
+      <c r="DA1" s="147"/>
+      <c r="DB1" s="147"/>
+      <c r="DC1" s="147"/>
+      <c r="DD1" s="147"/>
+      <c r="DE1" s="147"/>
+      <c r="DF1" s="147"/>
+      <c r="DG1" s="147"/>
+      <c r="DH1" s="147"/>
+      <c r="DI1" s="147"/>
+      <c r="DJ1" s="147"/>
+      <c r="DK1" s="147"/>
+      <c r="DL1" s="147"/>
+      <c r="DM1" s="147"/>
+      <c r="DN1" s="147"/>
+      <c r="DO1" s="147"/>
+      <c r="DP1" s="147"/>
+      <c r="DQ1" s="147"/>
+      <c r="DR1" s="147"/>
+      <c r="DS1" s="147"/>
+      <c r="DT1" s="147"/>
+      <c r="DU1" s="147"/>
+      <c r="DV1" s="147"/>
+      <c r="DW1" s="147"/>
+      <c r="DX1" s="147"/>
+      <c r="DY1" s="147"/>
+      <c r="DZ1" s="147"/>
+      <c r="EA1" s="147"/>
+      <c r="EB1" s="147"/>
+      <c r="EC1" s="147"/>
+      <c r="ED1" s="147"/>
+      <c r="EE1" s="147"/>
+      <c r="EF1" s="147"/>
+      <c r="EG1" s="147"/>
+      <c r="EH1" s="147"/>
+      <c r="EI1" s="147"/>
+      <c r="EJ1" s="147"/>
+      <c r="EK1" s="147"/>
+      <c r="EL1" s="147"/>
+      <c r="EM1" s="147"/>
+      <c r="EN1" s="147"/>
+      <c r="EO1" s="147"/>
     </row>
     <row r="2" spans="1:145" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="145"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="145"/>
-      <c r="T2" s="145"/>
-      <c r="U2" s="145"/>
-      <c r="V2" s="145"/>
-      <c r="W2" s="145"/>
-      <c r="X2" s="145"/>
-      <c r="Y2" s="145"/>
-      <c r="Z2" s="145"/>
-      <c r="AA2" s="145"/>
-      <c r="AB2" s="145"/>
-      <c r="AC2" s="145"/>
-      <c r="AD2" s="145"/>
-      <c r="AE2" s="145"/>
-      <c r="AF2" s="145"/>
-      <c r="AG2" s="145"/>
-      <c r="AH2" s="145"/>
-      <c r="AI2" s="145"/>
-      <c r="AJ2" s="145"/>
-      <c r="AK2" s="145"/>
-      <c r="AL2" s="145"/>
-      <c r="AM2" s="145"/>
-      <c r="AN2" s="145"/>
-      <c r="AO2" s="145"/>
-      <c r="AP2" s="145"/>
-      <c r="AQ2" s="145"/>
-      <c r="AR2" s="145"/>
-      <c r="AS2" s="145"/>
-      <c r="AT2" s="145"/>
-      <c r="AU2" s="145"/>
-      <c r="AV2" s="145"/>
-      <c r="AW2" s="145"/>
-      <c r="AX2" s="145"/>
-      <c r="AY2" s="145"/>
-      <c r="AZ2" s="145"/>
-      <c r="BA2" s="145"/>
-      <c r="BB2" s="145"/>
-      <c r="BC2" s="145"/>
-      <c r="BD2" s="145"/>
-      <c r="BE2" s="145"/>
-      <c r="BF2" s="145"/>
-      <c r="BG2" s="145"/>
-      <c r="BH2" s="145"/>
-      <c r="BI2" s="145"/>
-      <c r="BJ2" s="145"/>
-      <c r="BK2" s="145"/>
-      <c r="BL2" s="145"/>
-      <c r="BM2" s="145"/>
-      <c r="BN2" s="145"/>
-      <c r="BO2" s="145"/>
-      <c r="BP2" s="145"/>
-      <c r="BQ2" s="145"/>
-      <c r="BR2" s="145"/>
-      <c r="BS2" s="145"/>
-      <c r="BT2" s="145"/>
-      <c r="BU2" s="145"/>
-      <c r="BV2" s="145"/>
-      <c r="BW2" s="145"/>
-      <c r="BX2" s="145"/>
-      <c r="BY2" s="145"/>
-      <c r="BZ2" s="145"/>
-      <c r="CA2" s="145"/>
-      <c r="CB2" s="145"/>
-      <c r="CC2" s="145"/>
-      <c r="CD2" s="145"/>
-      <c r="CE2" s="145"/>
-      <c r="CF2" s="145"/>
-      <c r="CG2" s="145"/>
-      <c r="CH2" s="145"/>
-      <c r="CI2" s="145"/>
-      <c r="CJ2" s="145"/>
-      <c r="CK2" s="145"/>
-      <c r="CL2" s="145"/>
-      <c r="CM2" s="145"/>
-      <c r="CN2" s="145"/>
-      <c r="CO2" s="145"/>
-      <c r="CP2" s="145"/>
-      <c r="CQ2" s="145"/>
-      <c r="CR2" s="145"/>
-      <c r="CS2" s="145"/>
-      <c r="CT2" s="145"/>
-      <c r="CU2" s="145"/>
-      <c r="CV2" s="145"/>
-      <c r="CW2" s="145"/>
-      <c r="CX2" s="145"/>
-      <c r="CY2" s="145"/>
-      <c r="CZ2" s="145"/>
-      <c r="DA2" s="145"/>
-      <c r="DB2" s="145"/>
-      <c r="DC2" s="145"/>
-      <c r="DD2" s="145"/>
-      <c r="DE2" s="145"/>
-      <c r="DF2" s="145"/>
-      <c r="DG2" s="145"/>
-      <c r="DH2" s="145"/>
-      <c r="DI2" s="145"/>
-      <c r="DJ2" s="145"/>
-      <c r="DK2" s="145"/>
-      <c r="DL2" s="145"/>
-      <c r="DM2" s="145"/>
-      <c r="DN2" s="145"/>
-      <c r="DO2" s="145"/>
-      <c r="DP2" s="145"/>
-      <c r="DQ2" s="145"/>
-      <c r="DR2" s="145"/>
-      <c r="DS2" s="145"/>
-      <c r="DT2" s="145"/>
-      <c r="DU2" s="145"/>
-      <c r="DV2" s="145"/>
-      <c r="DW2" s="145"/>
-      <c r="DX2" s="145"/>
-      <c r="DY2" s="145"/>
-      <c r="DZ2" s="145"/>
-      <c r="EA2" s="145"/>
-      <c r="EB2" s="145"/>
-      <c r="EC2" s="145"/>
-      <c r="ED2" s="145"/>
-      <c r="EE2" s="145"/>
-      <c r="EF2" s="145"/>
-      <c r="EG2" s="145"/>
-      <c r="EH2" s="145"/>
-      <c r="EI2" s="145"/>
-      <c r="EJ2" s="145"/>
-      <c r="EK2" s="145"/>
-      <c r="EL2" s="145"/>
-      <c r="EM2" s="145"/>
-      <c r="EN2" s="145"/>
-      <c r="EO2" s="145"/>
-    </row>
-    <row r="3" spans="1:145" ht="27.95" customHeight="1">
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
+      <c r="Y2" s="147"/>
+      <c r="Z2" s="147"/>
+      <c r="AA2" s="147"/>
+      <c r="AB2" s="147"/>
+      <c r="AC2" s="147"/>
+      <c r="AD2" s="147"/>
+      <c r="AE2" s="147"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="147"/>
+      <c r="AH2" s="147"/>
+      <c r="AI2" s="147"/>
+      <c r="AJ2" s="147"/>
+      <c r="AK2" s="147"/>
+      <c r="AL2" s="147"/>
+      <c r="AM2" s="147"/>
+      <c r="AN2" s="147"/>
+      <c r="AO2" s="147"/>
+      <c r="AP2" s="147"/>
+      <c r="AQ2" s="147"/>
+      <c r="AR2" s="147"/>
+      <c r="AS2" s="147"/>
+      <c r="AT2" s="147"/>
+      <c r="AU2" s="147"/>
+      <c r="AV2" s="147"/>
+      <c r="AW2" s="147"/>
+      <c r="AX2" s="147"/>
+      <c r="AY2" s="147"/>
+      <c r="AZ2" s="147"/>
+      <c r="BA2" s="147"/>
+      <c r="BB2" s="147"/>
+      <c r="BC2" s="147"/>
+      <c r="BD2" s="147"/>
+      <c r="BE2" s="147"/>
+      <c r="BF2" s="147"/>
+      <c r="BG2" s="147"/>
+      <c r="BH2" s="147"/>
+      <c r="BI2" s="147"/>
+      <c r="BJ2" s="147"/>
+      <c r="BK2" s="147"/>
+      <c r="BL2" s="147"/>
+      <c r="BM2" s="147"/>
+      <c r="BN2" s="147"/>
+      <c r="BO2" s="147"/>
+      <c r="BP2" s="147"/>
+      <c r="BQ2" s="147"/>
+      <c r="BR2" s="147"/>
+      <c r="BS2" s="147"/>
+      <c r="BT2" s="147"/>
+      <c r="BU2" s="147"/>
+      <c r="BV2" s="147"/>
+      <c r="BW2" s="147"/>
+      <c r="BX2" s="147"/>
+      <c r="BY2" s="147"/>
+      <c r="BZ2" s="147"/>
+      <c r="CA2" s="147"/>
+      <c r="CB2" s="147"/>
+      <c r="CC2" s="147"/>
+      <c r="CD2" s="147"/>
+      <c r="CE2" s="147"/>
+      <c r="CF2" s="147"/>
+      <c r="CG2" s="147"/>
+      <c r="CH2" s="147"/>
+      <c r="CI2" s="147"/>
+      <c r="CJ2" s="147"/>
+      <c r="CK2" s="147"/>
+      <c r="CL2" s="147"/>
+      <c r="CM2" s="147"/>
+      <c r="CN2" s="147"/>
+      <c r="CO2" s="147"/>
+      <c r="CP2" s="147"/>
+      <c r="CQ2" s="147"/>
+      <c r="CR2" s="147"/>
+      <c r="CS2" s="147"/>
+      <c r="CT2" s="147"/>
+      <c r="CU2" s="147"/>
+      <c r="CV2" s="147"/>
+      <c r="CW2" s="147"/>
+      <c r="CX2" s="147"/>
+      <c r="CY2" s="147"/>
+      <c r="CZ2" s="147"/>
+      <c r="DA2" s="147"/>
+      <c r="DB2" s="147"/>
+      <c r="DC2" s="147"/>
+      <c r="DD2" s="147"/>
+      <c r="DE2" s="147"/>
+      <c r="DF2" s="147"/>
+      <c r="DG2" s="147"/>
+      <c r="DH2" s="147"/>
+      <c r="DI2" s="147"/>
+      <c r="DJ2" s="147"/>
+      <c r="DK2" s="147"/>
+      <c r="DL2" s="147"/>
+      <c r="DM2" s="147"/>
+      <c r="DN2" s="147"/>
+      <c r="DO2" s="147"/>
+      <c r="DP2" s="147"/>
+      <c r="DQ2" s="147"/>
+      <c r="DR2" s="147"/>
+      <c r="DS2" s="147"/>
+      <c r="DT2" s="147"/>
+      <c r="DU2" s="147"/>
+      <c r="DV2" s="147"/>
+      <c r="DW2" s="147"/>
+      <c r="DX2" s="147"/>
+      <c r="DY2" s="147"/>
+      <c r="DZ2" s="147"/>
+      <c r="EA2" s="147"/>
+      <c r="EB2" s="147"/>
+      <c r="EC2" s="147"/>
+      <c r="ED2" s="147"/>
+      <c r="EE2" s="147"/>
+      <c r="EF2" s="147"/>
+      <c r="EG2" s="147"/>
+      <c r="EH2" s="147"/>
+      <c r="EI2" s="147"/>
+      <c r="EJ2" s="147"/>
+      <c r="EK2" s="147"/>
+      <c r="EL2" s="147"/>
+      <c r="EM2" s="147"/>
+      <c r="EN2" s="147"/>
+      <c r="EO2" s="147"/>
+    </row>
+    <row r="3" spans="1:145" ht="27.9" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="148" t="s">
+      <c r="C3" s="147"/>
+      <c r="D3" s="181" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="148" t="s">
+      <c r="E3" s="147"/>
+      <c r="F3" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="145"/>
-      <c r="H3" s="148" t="s">
+      <c r="G3" s="147"/>
+      <c r="H3" s="181" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="145"/>
-      <c r="J3" s="148" t="s">
+      <c r="I3" s="147"/>
+      <c r="J3" s="181" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="145"/>
-      <c r="L3" s="148" t="s">
+      <c r="K3" s="147"/>
+      <c r="L3" s="181" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="151" t="s">
+      <c r="M3" s="147"/>
+      <c r="N3" s="189" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="145"/>
-      <c r="P3" s="151" t="s">
+      <c r="O3" s="147"/>
+      <c r="P3" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="151" t="s">
+      <c r="Q3" s="147"/>
+      <c r="R3" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="S3" s="145"/>
-      <c r="T3" s="151" t="s">
+      <c r="S3" s="147"/>
+      <c r="T3" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="U3" s="145"/>
-      <c r="V3" s="151" t="s">
+      <c r="U3" s="147"/>
+      <c r="V3" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="W3" s="145"/>
-      <c r="X3" s="151" t="s">
+      <c r="W3" s="147"/>
+      <c r="X3" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="Y3" s="145"/>
-      <c r="Z3" s="172" t="s">
+      <c r="Y3" s="147"/>
+      <c r="Z3" s="192" t="s">
         <v>47</v>
       </c>
-      <c r="AA3" s="145"/>
-      <c r="AB3" s="172" t="s">
+      <c r="AA3" s="147"/>
+      <c r="AB3" s="192" t="s">
         <v>48</v>
       </c>
-      <c r="AC3" s="145"/>
-      <c r="AD3" s="172" t="s">
+      <c r="AC3" s="147"/>
+      <c r="AD3" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="145"/>
-      <c r="AF3" s="172" t="s">
+      <c r="AE3" s="147"/>
+      <c r="AF3" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="AG3" s="145"/>
-      <c r="AH3" s="172" t="s">
+      <c r="AG3" s="147"/>
+      <c r="AH3" s="192" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="145"/>
-      <c r="AJ3" s="172" t="s">
+      <c r="AI3" s="147"/>
+      <c r="AJ3" s="192" t="s">
         <v>52</v>
       </c>
-      <c r="AK3" s="145"/>
-      <c r="AL3" s="149" t="s">
+      <c r="AK3" s="147"/>
+      <c r="AL3" s="191" t="s">
         <v>53</v>
       </c>
-      <c r="AM3" s="145"/>
-      <c r="AN3" s="149" t="s">
+      <c r="AM3" s="147"/>
+      <c r="AN3" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="AO3" s="145"/>
-      <c r="AP3" s="149" t="s">
+      <c r="AO3" s="147"/>
+      <c r="AP3" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="AQ3" s="145"/>
-      <c r="AR3" s="149" t="s">
+      <c r="AQ3" s="147"/>
+      <c r="AR3" s="191" t="s">
         <v>56</v>
       </c>
-      <c r="AS3" s="145"/>
-      <c r="AT3" s="149" t="s">
+      <c r="AS3" s="147"/>
+      <c r="AT3" s="191" t="s">
         <v>57</v>
       </c>
-      <c r="AU3" s="145"/>
-      <c r="AV3" s="149" t="s">
+      <c r="AU3" s="147"/>
+      <c r="AV3" s="191" t="s">
         <v>58</v>
       </c>
-      <c r="AW3" s="145"/>
-      <c r="AX3" s="150" t="s">
+      <c r="AW3" s="147"/>
+      <c r="AX3" s="183" t="s">
         <v>59</v>
       </c>
-      <c r="AY3" s="145"/>
-      <c r="AZ3" s="150" t="s">
+      <c r="AY3" s="147"/>
+      <c r="AZ3" s="183" t="s">
         <v>60</v>
       </c>
-      <c r="BA3" s="145"/>
-      <c r="BB3" s="150" t="s">
+      <c r="BA3" s="147"/>
+      <c r="BB3" s="183" t="s">
         <v>61</v>
       </c>
-      <c r="BC3" s="145"/>
-      <c r="BD3" s="150" t="s">
+      <c r="BC3" s="147"/>
+      <c r="BD3" s="183" t="s">
         <v>62</v>
       </c>
-      <c r="BE3" s="145"/>
-      <c r="BF3" s="150" t="s">
+      <c r="BE3" s="147"/>
+      <c r="BF3" s="183" t="s">
         <v>63</v>
       </c>
-      <c r="BG3" s="145"/>
-      <c r="BH3" s="150" t="s">
+      <c r="BG3" s="147"/>
+      <c r="BH3" s="183" t="s">
         <v>64</v>
       </c>
-      <c r="BI3" s="145"/>
-      <c r="BJ3" s="153" t="s">
+      <c r="BI3" s="147"/>
+      <c r="BJ3" s="184" t="s">
         <v>65</v>
       </c>
-      <c r="BK3" s="145"/>
-      <c r="BL3" s="153" t="s">
+      <c r="BK3" s="147"/>
+      <c r="BL3" s="184" t="s">
         <v>66</v>
       </c>
-      <c r="BM3" s="145"/>
-      <c r="BN3" s="153" t="s">
+      <c r="BM3" s="147"/>
+      <c r="BN3" s="184" t="s">
         <v>67</v>
       </c>
-      <c r="BO3" s="145"/>
-      <c r="BP3" s="153" t="s">
+      <c r="BO3" s="147"/>
+      <c r="BP3" s="184" t="s">
         <v>68</v>
       </c>
-      <c r="BQ3" s="145"/>
-      <c r="BR3" s="153" t="s">
+      <c r="BQ3" s="147"/>
+      <c r="BR3" s="184" t="s">
         <v>69</v>
       </c>
-      <c r="BS3" s="145"/>
-      <c r="BT3" s="153" t="s">
+      <c r="BS3" s="147"/>
+      <c r="BT3" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="BU3" s="145"/>
-      <c r="BV3" s="154" t="s">
+      <c r="BU3" s="147"/>
+      <c r="BV3" s="199" t="s">
         <v>71</v>
       </c>
-      <c r="BW3" s="145"/>
-      <c r="BX3" s="154" t="s">
+      <c r="BW3" s="147"/>
+      <c r="BX3" s="199" t="s">
         <v>72</v>
       </c>
-      <c r="BY3" s="145"/>
-      <c r="BZ3" s="154" t="s">
+      <c r="BY3" s="147"/>
+      <c r="BZ3" s="199" t="s">
         <v>73</v>
       </c>
-      <c r="CA3" s="145"/>
-      <c r="CB3" s="154" t="s">
+      <c r="CA3" s="147"/>
+      <c r="CB3" s="199" t="s">
         <v>74</v>
       </c>
-      <c r="CC3" s="145"/>
-      <c r="CD3" s="154" t="s">
+      <c r="CC3" s="147"/>
+      <c r="CD3" s="199" t="s">
         <v>75</v>
       </c>
-      <c r="CE3" s="145"/>
-      <c r="CF3" s="154" t="s">
+      <c r="CE3" s="147"/>
+      <c r="CF3" s="199" t="s">
         <v>76</v>
       </c>
-      <c r="CG3" s="145"/>
-      <c r="CH3" s="157" t="s">
+      <c r="CG3" s="147"/>
+      <c r="CH3" s="195" t="s">
         <v>77</v>
       </c>
-      <c r="CI3" s="145"/>
-      <c r="CJ3" s="157" t="s">
+      <c r="CI3" s="147"/>
+      <c r="CJ3" s="195" t="s">
         <v>78</v>
       </c>
-      <c r="CK3" s="145"/>
-      <c r="CL3" s="157" t="s">
+      <c r="CK3" s="147"/>
+      <c r="CL3" s="195" t="s">
         <v>79</v>
       </c>
-      <c r="CM3" s="145"/>
-      <c r="CN3" s="157" t="s">
+      <c r="CM3" s="147"/>
+      <c r="CN3" s="195" t="s">
         <v>80</v>
       </c>
-      <c r="CO3" s="145"/>
-      <c r="CP3" s="157" t="s">
+      <c r="CO3" s="147"/>
+      <c r="CP3" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="CQ3" s="145"/>
-      <c r="CR3" s="157" t="s">
+      <c r="CQ3" s="147"/>
+      <c r="CR3" s="195" t="s">
         <v>82</v>
       </c>
-      <c r="CS3" s="145"/>
-      <c r="CT3" s="158" t="s">
+      <c r="CS3" s="147"/>
+      <c r="CT3" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="CU3" s="145"/>
-      <c r="CV3" s="158" t="s">
+      <c r="CU3" s="147"/>
+      <c r="CV3" s="178" t="s">
         <v>84</v>
       </c>
-      <c r="CW3" s="145"/>
-      <c r="CX3" s="158" t="s">
+      <c r="CW3" s="147"/>
+      <c r="CX3" s="178" t="s">
         <v>85</v>
       </c>
-      <c r="CY3" s="145"/>
-      <c r="CZ3" s="158" t="s">
+      <c r="CY3" s="147"/>
+      <c r="CZ3" s="178" t="s">
         <v>86</v>
       </c>
-      <c r="DA3" s="145"/>
-      <c r="DB3" s="158" t="s">
+      <c r="DA3" s="147"/>
+      <c r="DB3" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="DC3" s="145"/>
-      <c r="DD3" s="158" t="s">
+      <c r="DC3" s="147"/>
+      <c r="DD3" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="DE3" s="145"/>
-      <c r="DF3" s="161" t="s">
+      <c r="DE3" s="147"/>
+      <c r="DF3" s="198" t="s">
         <v>89</v>
       </c>
-      <c r="DG3" s="145"/>
-      <c r="DH3" s="161" t="s">
+      <c r="DG3" s="147"/>
+      <c r="DH3" s="198" t="s">
         <v>90</v>
       </c>
-      <c r="DI3" s="145"/>
-      <c r="DJ3" s="161" t="s">
+      <c r="DI3" s="147"/>
+      <c r="DJ3" s="198" t="s">
         <v>91</v>
       </c>
-      <c r="DK3" s="145"/>
-      <c r="DL3" s="161" t="s">
+      <c r="DK3" s="147"/>
+      <c r="DL3" s="198" t="s">
         <v>92</v>
       </c>
-      <c r="DM3" s="145"/>
-      <c r="DN3" s="161" t="s">
+      <c r="DM3" s="147"/>
+      <c r="DN3" s="198" t="s">
         <v>93</v>
       </c>
-      <c r="DO3" s="145"/>
-      <c r="DP3" s="161" t="s">
+      <c r="DO3" s="147"/>
+      <c r="DP3" s="198" t="s">
         <v>94</v>
       </c>
-      <c r="DQ3" s="145"/>
-      <c r="DR3" s="160" t="s">
+      <c r="DQ3" s="147"/>
+      <c r="DR3" s="188" t="s">
         <v>95</v>
       </c>
-      <c r="DS3" s="145"/>
-      <c r="DT3" s="160" t="s">
+      <c r="DS3" s="147"/>
+      <c r="DT3" s="188" t="s">
         <v>96</v>
       </c>
-      <c r="DU3" s="145"/>
-      <c r="DV3" s="160" t="s">
+      <c r="DU3" s="147"/>
+      <c r="DV3" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="DW3" s="145"/>
-      <c r="DX3" s="160" t="s">
+      <c r="DW3" s="147"/>
+      <c r="DX3" s="188" t="s">
         <v>98</v>
       </c>
-      <c r="DY3" s="145"/>
-      <c r="DZ3" s="160" t="s">
+      <c r="DY3" s="147"/>
+      <c r="DZ3" s="188" t="s">
         <v>99</v>
       </c>
-      <c r="EA3" s="145"/>
-      <c r="EB3" s="160" t="s">
+      <c r="EA3" s="147"/>
+      <c r="EB3" s="188" t="s">
         <v>100</v>
       </c>
-      <c r="EC3" s="145"/>
-      <c r="ED3" s="156" t="s">
+      <c r="EC3" s="147"/>
+      <c r="ED3" s="177" t="s">
         <v>101</v>
       </c>
-      <c r="EE3" s="145"/>
-      <c r="EF3" s="156" t="s">
+      <c r="EE3" s="147"/>
+      <c r="EF3" s="177" t="s">
         <v>102</v>
       </c>
-      <c r="EG3" s="145"/>
-      <c r="EH3" s="156" t="s">
+      <c r="EG3" s="147"/>
+      <c r="EH3" s="177" t="s">
         <v>103</v>
       </c>
-      <c r="EI3" s="145"/>
-      <c r="EJ3" s="156" t="s">
+      <c r="EI3" s="147"/>
+      <c r="EJ3" s="177" t="s">
         <v>104</v>
       </c>
-      <c r="EK3" s="145"/>
-      <c r="EL3" s="156" t="s">
+      <c r="EK3" s="147"/>
+      <c r="EL3" s="177" t="s">
         <v>105</v>
       </c>
-      <c r="EM3" s="145"/>
-      <c r="EN3" s="156" t="s">
+      <c r="EM3" s="147"/>
+      <c r="EN3" s="177" t="s">
         <v>106</v>
       </c>
-      <c r="EO3" s="145"/>
+      <c r="EO3" s="147"/>
     </row>
     <row r="4" spans="1:145" ht="26.1" customHeight="1">
       <c r="A4" s="18" t="s">
@@ -8085,7 +8082,7 @@
     </row>
     <row r="5" spans="1:145">
       <c r="A5" s="19" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B5" s="126">
         <v>2</v>
@@ -8520,123 +8517,123 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:145" ht="21.95" customHeight="1">
-      <c r="A7" s="177" t="s">
+    <row r="7" spans="1:145" ht="21.9" customHeight="1">
+      <c r="A7" s="179" t="s">
         <v>1598</v>
       </c>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="145"/>
-      <c r="J7" s="145"/>
-      <c r="K7" s="145"/>
-      <c r="L7" s="145"/>
-      <c r="M7" s="145"/>
-      <c r="N7" s="145"/>
-      <c r="O7" s="145"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
-      <c r="R7" s="145"/>
-      <c r="S7" s="145"/>
-      <c r="T7" s="145"/>
-      <c r="U7" s="145"/>
-      <c r="V7" s="145"/>
-      <c r="W7" s="145"/>
-      <c r="X7" s="145"/>
-      <c r="Y7" s="145"/>
-      <c r="Z7" s="145"/>
-      <c r="AA7" s="145"/>
-      <c r="AB7" s="145"/>
-      <c r="AC7" s="145"/>
-      <c r="AD7" s="145"/>
-      <c r="AE7" s="145"/>
-      <c r="AF7" s="145"/>
-      <c r="AG7" s="145"/>
-      <c r="AH7" s="145"/>
-      <c r="AI7" s="145"/>
-      <c r="AJ7" s="145"/>
-      <c r="AK7" s="145"/>
-      <c r="AL7" s="145"/>
-      <c r="AM7" s="145"/>
-      <c r="AN7" s="145"/>
-      <c r="AO7" s="145"/>
-      <c r="AP7" s="145"/>
-      <c r="AQ7" s="145"/>
-      <c r="AR7" s="145"/>
-      <c r="AS7" s="145"/>
-      <c r="AT7" s="145"/>
-      <c r="AU7" s="145"/>
-      <c r="AV7" s="145"/>
-    </row>
-    <row r="8" spans="1:145" ht="21.95" customHeight="1">
-      <c r="A8" s="171" t="s">
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
+      <c r="U7" s="147"/>
+      <c r="V7" s="147"/>
+      <c r="W7" s="147"/>
+      <c r="X7" s="147"/>
+      <c r="Y7" s="147"/>
+      <c r="Z7" s="147"/>
+      <c r="AA7" s="147"/>
+      <c r="AB7" s="147"/>
+      <c r="AC7" s="147"/>
+      <c r="AD7" s="147"/>
+      <c r="AE7" s="147"/>
+      <c r="AF7" s="147"/>
+      <c r="AG7" s="147"/>
+      <c r="AH7" s="147"/>
+      <c r="AI7" s="147"/>
+      <c r="AJ7" s="147"/>
+      <c r="AK7" s="147"/>
+      <c r="AL7" s="147"/>
+      <c r="AM7" s="147"/>
+      <c r="AN7" s="147"/>
+      <c r="AO7" s="147"/>
+      <c r="AP7" s="147"/>
+      <c r="AQ7" s="147"/>
+      <c r="AR7" s="147"/>
+      <c r="AS7" s="147"/>
+      <c r="AT7" s="147"/>
+      <c r="AU7" s="147"/>
+      <c r="AV7" s="147"/>
+    </row>
+    <row r="8" spans="1:145" ht="21.9" customHeight="1">
+      <c r="A8" s="200" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="145"/>
-      <c r="H8" s="145"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="145"/>
-      <c r="K8" s="145"/>
-      <c r="L8" s="145"/>
-      <c r="M8" s="145"/>
-      <c r="N8" s="145"/>
-      <c r="O8" s="145"/>
-      <c r="Q8" s="166" t="s">
+      <c r="B8" s="147"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="147"/>
+      <c r="O8" s="147"/>
+      <c r="Q8" s="201" t="s">
         <v>157</v>
       </c>
-      <c r="R8" s="145"/>
-      <c r="S8" s="145"/>
-      <c r="T8" s="145"/>
-      <c r="U8" s="145"/>
-      <c r="V8" s="145"/>
-      <c r="W8" s="145"/>
-      <c r="X8" s="145"/>
-      <c r="Y8" s="145"/>
-      <c r="Z8" s="145"/>
-      <c r="AA8" s="145"/>
-      <c r="AB8" s="145"/>
-      <c r="AC8" s="145"/>
-      <c r="AD8" s="145"/>
-      <c r="AE8" s="145"/>
-      <c r="AG8" s="159" t="s">
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="147"/>
+      <c r="U8" s="147"/>
+      <c r="V8" s="147"/>
+      <c r="W8" s="147"/>
+      <c r="X8" s="147"/>
+      <c r="Y8" s="147"/>
+      <c r="Z8" s="147"/>
+      <c r="AA8" s="147"/>
+      <c r="AB8" s="147"/>
+      <c r="AC8" s="147"/>
+      <c r="AD8" s="147"/>
+      <c r="AE8" s="147"/>
+      <c r="AG8" s="204" t="s">
         <v>158</v>
       </c>
-      <c r="AH8" s="145"/>
-      <c r="AI8" s="145"/>
-      <c r="AJ8" s="145"/>
-      <c r="AK8" s="145"/>
-      <c r="AL8" s="145"/>
-      <c r="AM8" s="145"/>
-      <c r="AN8" s="145"/>
-      <c r="AO8" s="145"/>
-      <c r="AP8" s="145"/>
-      <c r="AQ8" s="145"/>
-      <c r="AR8" s="145"/>
-      <c r="AS8" s="145"/>
-      <c r="AT8" s="145"/>
-      <c r="AU8" s="145"/>
+      <c r="AH8" s="147"/>
+      <c r="AI8" s="147"/>
+      <c r="AJ8" s="147"/>
+      <c r="AK8" s="147"/>
+      <c r="AL8" s="147"/>
+      <c r="AM8" s="147"/>
+      <c r="AN8" s="147"/>
+      <c r="AO8" s="147"/>
+      <c r="AP8" s="147"/>
+      <c r="AQ8" s="147"/>
+      <c r="AR8" s="147"/>
+      <c r="AS8" s="147"/>
+      <c r="AT8" s="147"/>
+      <c r="AU8" s="147"/>
     </row>
     <row r="9" spans="1:145" ht="18" customHeight="1">
       <c r="A9" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C9" s="145"/>
-      <c r="D9" s="145"/>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="147"/>
       <c r="H9" s="21" t="s">
         <v>160</v>
       </c>
@@ -8667,14 +8664,14 @@
       <c r="Q9" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R9" s="167" t="s">
+      <c r="R9" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S9" s="145"/>
-      <c r="T9" s="145"/>
-      <c r="U9" s="145"/>
-      <c r="V9" s="145"/>
-      <c r="W9" s="145"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="147"/>
+      <c r="U9" s="147"/>
+      <c r="V9" s="147"/>
+      <c r="W9" s="147"/>
       <c r="X9" s="21" t="s">
         <v>160</v>
       </c>
@@ -8705,14 +8702,14 @@
       <c r="AG9" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH9" s="167" t="s">
+      <c r="AH9" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI9" s="145"/>
-      <c r="AJ9" s="145"/>
-      <c r="AK9" s="145"/>
-      <c r="AL9" s="145"/>
-      <c r="AM9" s="145"/>
+      <c r="AI9" s="147"/>
+      <c r="AJ9" s="147"/>
+      <c r="AK9" s="147"/>
+      <c r="AL9" s="147"/>
+      <c r="AM9" s="147"/>
       <c r="AN9" s="21" t="s">
         <v>160</v>
       </c>
@@ -8745,15 +8742,15 @@
       <c r="A10" s="22">
         <v>1</v>
       </c>
-      <c r="B10" s="163" t="str">
+      <c r="B10" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(1,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Mexico</v>
       </c>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="145"/>
-      <c r="F10" s="145"/>
-      <c r="G10" s="145"/>
+      <c r="C10" s="147"/>
+      <c r="D10" s="147"/>
+      <c r="E10" s="147"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="147"/>
       <c r="H10" s="23">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(1,Calc!$J$3:$J$6,0)),0)</f>
         <v>9</v>
@@ -8793,15 +8790,15 @@
       <c r="Q10" s="22">
         <v>1</v>
       </c>
-      <c r="R10" s="163" t="str">
+      <c r="R10" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(1,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Suica</v>
       </c>
-      <c r="S10" s="145"/>
-      <c r="T10" s="145"/>
-      <c r="U10" s="145"/>
-      <c r="V10" s="145"/>
-      <c r="W10" s="145"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="147"/>
+      <c r="U10" s="147"/>
+      <c r="V10" s="147"/>
+      <c r="W10" s="147"/>
       <c r="X10" s="23">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(1,Calc!$J$7:$J$10,0)),0)</f>
         <v>7</v>
@@ -8841,15 +8838,15 @@
       <c r="AG10" s="22">
         <v>1</v>
       </c>
-      <c r="AH10" s="163" t="str">
+      <c r="AH10" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(1,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Brasil</v>
       </c>
-      <c r="AI10" s="145"/>
-      <c r="AJ10" s="145"/>
-      <c r="AK10" s="145"/>
-      <c r="AL10" s="145"/>
-      <c r="AM10" s="145"/>
+      <c r="AI10" s="147"/>
+      <c r="AJ10" s="147"/>
+      <c r="AK10" s="147"/>
+      <c r="AL10" s="147"/>
+      <c r="AM10" s="147"/>
       <c r="AN10" s="23">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(1,Calc!$J$11:$J$14,0)),0)</f>
         <v>9</v>
@@ -8891,15 +8888,15 @@
       <c r="A11" s="24">
         <v>2</v>
       </c>
-      <c r="B11" s="152" t="str">
+      <c r="B11" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(2,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Coreia do Sul</v>
       </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
       <c r="H11" s="25">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(2,Calc!$J$3:$J$6,0)),0)</f>
         <v>4</v>
@@ -8939,15 +8936,15 @@
       <c r="Q11" s="24">
         <v>2</v>
       </c>
-      <c r="R11" s="152" t="str">
+      <c r="R11" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(2,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Canada</v>
       </c>
-      <c r="S11" s="145"/>
-      <c r="T11" s="145"/>
-      <c r="U11" s="145"/>
-      <c r="V11" s="145"/>
-      <c r="W11" s="145"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="147"/>
+      <c r="U11" s="147"/>
+      <c r="V11" s="147"/>
+      <c r="W11" s="147"/>
       <c r="X11" s="25">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(2,Calc!$J$7:$J$10,0)),0)</f>
         <v>7</v>
@@ -8987,15 +8984,15 @@
       <c r="AG11" s="24">
         <v>2</v>
       </c>
-      <c r="AH11" s="152" t="str">
+      <c r="AH11" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(2,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Marrocos</v>
       </c>
-      <c r="AI11" s="145"/>
-      <c r="AJ11" s="145"/>
-      <c r="AK11" s="145"/>
-      <c r="AL11" s="145"/>
-      <c r="AM11" s="145"/>
+      <c r="AI11" s="147"/>
+      <c r="AJ11" s="147"/>
+      <c r="AK11" s="147"/>
+      <c r="AL11" s="147"/>
+      <c r="AM11" s="147"/>
       <c r="AN11" s="25">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(2,Calc!$J$11:$J$14,0)),0)</f>
         <v>4</v>
@@ -9037,15 +9034,15 @@
       <c r="A12" s="26">
         <v>3</v>
       </c>
-      <c r="B12" s="165" t="str">
+      <c r="B12" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(3,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Tchequia</v>
       </c>
-      <c r="C12" s="145"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="145"/>
-      <c r="F12" s="145"/>
-      <c r="G12" s="145"/>
+      <c r="C12" s="147"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="147"/>
       <c r="H12" s="27">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(3,Calc!$J$3:$J$6,0)),0)</f>
         <v>4</v>
@@ -9085,15 +9082,15 @@
       <c r="Q12" s="26">
         <v>3</v>
       </c>
-      <c r="R12" s="165" t="str">
+      <c r="R12" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(3,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Bosnia e Herzegovina</v>
       </c>
-      <c r="S12" s="145"/>
-      <c r="T12" s="145"/>
-      <c r="U12" s="145"/>
-      <c r="V12" s="145"/>
-      <c r="W12" s="145"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="147"/>
+      <c r="U12" s="147"/>
+      <c r="V12" s="147"/>
+      <c r="W12" s="147"/>
       <c r="X12" s="27">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(3,Calc!$J$7:$J$10,0)),0)</f>
         <v>3</v>
@@ -9133,15 +9130,15 @@
       <c r="AG12" s="26">
         <v>3</v>
       </c>
-      <c r="AH12" s="165" t="str">
+      <c r="AH12" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(3,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Escocia</v>
       </c>
-      <c r="AI12" s="145"/>
-      <c r="AJ12" s="145"/>
-      <c r="AK12" s="145"/>
-      <c r="AL12" s="145"/>
-      <c r="AM12" s="145"/>
+      <c r="AI12" s="147"/>
+      <c r="AJ12" s="147"/>
+      <c r="AK12" s="147"/>
+      <c r="AL12" s="147"/>
+      <c r="AM12" s="147"/>
       <c r="AN12" s="27">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(3,Calc!$J$11:$J$14,0)),0)</f>
         <v>4</v>
@@ -9183,15 +9180,15 @@
       <c r="A13" s="28">
         <v>4</v>
       </c>
-      <c r="B13" s="164" t="str">
+      <c r="B13" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$3:$B$6,MATCH(4,Calc!$J$3:$J$6,0)),"?")</f>
         <v>Africa do Sul</v>
       </c>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="145"/>
-      <c r="F13" s="145"/>
-      <c r="G13" s="145"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="147"/>
       <c r="H13" s="29">
         <f>IFERROR(INDEX(Calc!$H$3:$H$6,MATCH(4,Calc!$J$3:$J$6,0)),0)</f>
         <v>0</v>
@@ -9231,15 +9228,15 @@
       <c r="Q13" s="28">
         <v>4</v>
       </c>
-      <c r="R13" s="164" t="str">
+      <c r="R13" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$7:$B$10,MATCH(4,Calc!$J$7:$J$10,0)),"?")</f>
         <v>Qatar</v>
       </c>
-      <c r="S13" s="145"/>
-      <c r="T13" s="145"/>
-      <c r="U13" s="145"/>
-      <c r="V13" s="145"/>
-      <c r="W13" s="145"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="147"/>
+      <c r="U13" s="147"/>
+      <c r="V13" s="147"/>
+      <c r="W13" s="147"/>
       <c r="X13" s="29">
         <f>IFERROR(INDEX(Calc!$H$7:$H$10,MATCH(4,Calc!$J$7:$J$10,0)),0)</f>
         <v>0</v>
@@ -9279,15 +9276,15 @@
       <c r="AG13" s="28">
         <v>4</v>
       </c>
-      <c r="AH13" s="164" t="str">
+      <c r="AH13" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$11:$B$14,MATCH(4,Calc!$J$11:$J$14,0)),"?")</f>
         <v>Haiti</v>
       </c>
-      <c r="AI13" s="145"/>
-      <c r="AJ13" s="145"/>
-      <c r="AK13" s="145"/>
-      <c r="AL13" s="145"/>
-      <c r="AM13" s="145"/>
+      <c r="AI13" s="147"/>
+      <c r="AJ13" s="147"/>
+      <c r="AK13" s="147"/>
+      <c r="AL13" s="147"/>
+      <c r="AM13" s="147"/>
       <c r="AN13" s="29">
         <f>IFERROR(INDEX(Calc!$H$11:$H$14,MATCH(4,Calc!$J$11:$J$14,0)),0)</f>
         <v>0</v>
@@ -9325,71 +9322,71 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:145" ht="21.95" customHeight="1">
-      <c r="A15" s="162" t="s">
+    <row r="15" spans="1:145" ht="21.9" customHeight="1">
+      <c r="A15" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="145"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="145"/>
-      <c r="F15" s="145"/>
-      <c r="G15" s="145"/>
-      <c r="H15" s="145"/>
-      <c r="I15" s="145"/>
-      <c r="J15" s="145"/>
-      <c r="K15" s="145"/>
-      <c r="L15" s="145"/>
-      <c r="M15" s="145"/>
-      <c r="N15" s="145"/>
-      <c r="O15" s="145"/>
-      <c r="Q15" s="179" t="s">
+      <c r="B15" s="147"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="147"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="147"/>
+      <c r="I15" s="147"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="147"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="147"/>
+      <c r="Q15" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="R15" s="145"/>
-      <c r="S15" s="145"/>
-      <c r="T15" s="145"/>
-      <c r="U15" s="145"/>
-      <c r="V15" s="145"/>
-      <c r="W15" s="145"/>
-      <c r="X15" s="145"/>
-      <c r="Y15" s="145"/>
-      <c r="Z15" s="145"/>
-      <c r="AA15" s="145"/>
-      <c r="AB15" s="145"/>
-      <c r="AC15" s="145"/>
-      <c r="AD15" s="145"/>
-      <c r="AE15" s="145"/>
-      <c r="AG15" s="155" t="s">
+      <c r="R15" s="147"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="147"/>
+      <c r="U15" s="147"/>
+      <c r="V15" s="147"/>
+      <c r="W15" s="147"/>
+      <c r="X15" s="147"/>
+      <c r="Y15" s="147"/>
+      <c r="Z15" s="147"/>
+      <c r="AA15" s="147"/>
+      <c r="AB15" s="147"/>
+      <c r="AC15" s="147"/>
+      <c r="AD15" s="147"/>
+      <c r="AE15" s="147"/>
+      <c r="AG15" s="205" t="s">
         <v>171</v>
       </c>
-      <c r="AH15" s="145"/>
-      <c r="AI15" s="145"/>
-      <c r="AJ15" s="145"/>
-      <c r="AK15" s="145"/>
-      <c r="AL15" s="145"/>
-      <c r="AM15" s="145"/>
-      <c r="AN15" s="145"/>
-      <c r="AO15" s="145"/>
-      <c r="AP15" s="145"/>
-      <c r="AQ15" s="145"/>
-      <c r="AR15" s="145"/>
-      <c r="AS15" s="145"/>
-      <c r="AT15" s="145"/>
-      <c r="AU15" s="145"/>
+      <c r="AH15" s="147"/>
+      <c r="AI15" s="147"/>
+      <c r="AJ15" s="147"/>
+      <c r="AK15" s="147"/>
+      <c r="AL15" s="147"/>
+      <c r="AM15" s="147"/>
+      <c r="AN15" s="147"/>
+      <c r="AO15" s="147"/>
+      <c r="AP15" s="147"/>
+      <c r="AQ15" s="147"/>
+      <c r="AR15" s="147"/>
+      <c r="AS15" s="147"/>
+      <c r="AT15" s="147"/>
+      <c r="AU15" s="147"/>
     </row>
     <row r="16" spans="1:145" ht="18" customHeight="1">
       <c r="A16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="167" t="s">
+      <c r="B16" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="145"/>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="147"/>
       <c r="H16" s="21" t="s">
         <v>160</v>
       </c>
@@ -9420,14 +9417,14 @@
       <c r="Q16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R16" s="167" t="s">
+      <c r="R16" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S16" s="145"/>
-      <c r="T16" s="145"/>
-      <c r="U16" s="145"/>
-      <c r="V16" s="145"/>
-      <c r="W16" s="145"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
+      <c r="U16" s="147"/>
+      <c r="V16" s="147"/>
+      <c r="W16" s="147"/>
       <c r="X16" s="21" t="s">
         <v>160</v>
       </c>
@@ -9458,14 +9455,14 @@
       <c r="AG16" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH16" s="167" t="s">
+      <c r="AH16" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI16" s="145"/>
-      <c r="AJ16" s="145"/>
-      <c r="AK16" s="145"/>
-      <c r="AL16" s="145"/>
-      <c r="AM16" s="145"/>
+      <c r="AI16" s="147"/>
+      <c r="AJ16" s="147"/>
+      <c r="AK16" s="147"/>
+      <c r="AL16" s="147"/>
+      <c r="AM16" s="147"/>
       <c r="AN16" s="21" t="s">
         <v>160</v>
       </c>
@@ -9498,15 +9495,15 @@
       <c r="A17" s="22">
         <v>1</v>
       </c>
-      <c r="B17" s="163" t="str">
+      <c r="B17" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(1,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Estados Unidos</v>
       </c>
-      <c r="C17" s="145"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="145"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="145"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
       <c r="H17" s="23">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(1,Calc!$J$15:$J$18,0)),0)</f>
         <v>9</v>
@@ -9546,15 +9543,15 @@
       <c r="Q17" s="22">
         <v>1</v>
       </c>
-      <c r="R17" s="163" t="str">
+      <c r="R17" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(1,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Alemanha</v>
       </c>
-      <c r="S17" s="145"/>
-      <c r="T17" s="145"/>
-      <c r="U17" s="145"/>
-      <c r="V17" s="145"/>
-      <c r="W17" s="145"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="147"/>
+      <c r="U17" s="147"/>
+      <c r="V17" s="147"/>
+      <c r="W17" s="147"/>
       <c r="X17" s="23">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(1,Calc!$J$19:$J$22,0)),0)</f>
         <v>9</v>
@@ -9594,15 +9591,15 @@
       <c r="AG17" s="22">
         <v>1</v>
       </c>
-      <c r="AH17" s="163" t="str">
+      <c r="AH17" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(1,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Holanda</v>
       </c>
-      <c r="AI17" s="145"/>
-      <c r="AJ17" s="145"/>
-      <c r="AK17" s="145"/>
-      <c r="AL17" s="145"/>
-      <c r="AM17" s="145"/>
+      <c r="AI17" s="147"/>
+      <c r="AJ17" s="147"/>
+      <c r="AK17" s="147"/>
+      <c r="AL17" s="147"/>
+      <c r="AM17" s="147"/>
       <c r="AN17" s="23">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(1,Calc!$J$23:$J$26,0)),0)</f>
         <v>9</v>
@@ -9644,15 +9641,15 @@
       <c r="A18" s="24">
         <v>2</v>
       </c>
-      <c r="B18" s="152" t="str">
+      <c r="B18" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(2,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Turquia</v>
       </c>
-      <c r="C18" s="145"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="145"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="145"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="147"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="147"/>
       <c r="H18" s="25">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(2,Calc!$J$15:$J$18,0)),0)</f>
         <v>4</v>
@@ -9692,15 +9689,15 @@
       <c r="Q18" s="24">
         <v>2</v>
       </c>
-      <c r="R18" s="152" t="str">
+      <c r="R18" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(2,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Equador</v>
       </c>
-      <c r="S18" s="145"/>
-      <c r="T18" s="145"/>
-      <c r="U18" s="145"/>
-      <c r="V18" s="145"/>
-      <c r="W18" s="145"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="147"/>
+      <c r="U18" s="147"/>
+      <c r="V18" s="147"/>
+      <c r="W18" s="147"/>
       <c r="X18" s="25">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(2,Calc!$J$19:$J$22,0)),0)</f>
         <v>4</v>
@@ -9740,15 +9737,15 @@
       <c r="AG18" s="24">
         <v>2</v>
       </c>
-      <c r="AH18" s="152" t="str">
+      <c r="AH18" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(2,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Japao</v>
       </c>
-      <c r="AI18" s="145"/>
-      <c r="AJ18" s="145"/>
-      <c r="AK18" s="145"/>
-      <c r="AL18" s="145"/>
-      <c r="AM18" s="145"/>
+      <c r="AI18" s="147"/>
+      <c r="AJ18" s="147"/>
+      <c r="AK18" s="147"/>
+      <c r="AL18" s="147"/>
+      <c r="AM18" s="147"/>
       <c r="AN18" s="25">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(2,Calc!$J$23:$J$26,0)),0)</f>
         <v>4</v>
@@ -9790,15 +9787,15 @@
       <c r="A19" s="26">
         <v>3</v>
       </c>
-      <c r="B19" s="165" t="str">
+      <c r="B19" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(3,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Paraguai</v>
       </c>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="145"/>
+      <c r="C19" s="147"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="147"/>
+      <c r="F19" s="147"/>
+      <c r="G19" s="147"/>
       <c r="H19" s="27">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(3,Calc!$J$15:$J$18,0)),0)</f>
         <v>4</v>
@@ -9838,15 +9835,15 @@
       <c r="Q19" s="26">
         <v>3</v>
       </c>
-      <c r="R19" s="165" t="str">
+      <c r="R19" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(3,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Costa do Marfim</v>
       </c>
-      <c r="S19" s="145"/>
-      <c r="T19" s="145"/>
-      <c r="U19" s="145"/>
-      <c r="V19" s="145"/>
-      <c r="W19" s="145"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="147"/>
+      <c r="W19" s="147"/>
       <c r="X19" s="27">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(3,Calc!$J$19:$J$22,0)),0)</f>
         <v>4</v>
@@ -9886,15 +9883,15 @@
       <c r="AG19" s="26">
         <v>3</v>
       </c>
-      <c r="AH19" s="165" t="str">
+      <c r="AH19" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(3,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Suecia</v>
       </c>
-      <c r="AI19" s="145"/>
-      <c r="AJ19" s="145"/>
-      <c r="AK19" s="145"/>
-      <c r="AL19" s="145"/>
-      <c r="AM19" s="145"/>
+      <c r="AI19" s="147"/>
+      <c r="AJ19" s="147"/>
+      <c r="AK19" s="147"/>
+      <c r="AL19" s="147"/>
+      <c r="AM19" s="147"/>
       <c r="AN19" s="27">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(3,Calc!$J$23:$J$26,0)),0)</f>
         <v>4</v>
@@ -9936,15 +9933,15 @@
       <c r="A20" s="28">
         <v>4</v>
       </c>
-      <c r="B20" s="164" t="str">
+      <c r="B20" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$15:$B$18,MATCH(4,Calc!$J$15:$J$18,0)),"?")</f>
         <v>Australia</v>
       </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="145"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="145"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="147"/>
+      <c r="G20" s="147"/>
       <c r="H20" s="29">
         <f>IFERROR(INDEX(Calc!$H$15:$H$18,MATCH(4,Calc!$J$15:$J$18,0)),0)</f>
         <v>0</v>
@@ -9984,15 +9981,15 @@
       <c r="Q20" s="28">
         <v>4</v>
       </c>
-      <c r="R20" s="164" t="str">
+      <c r="R20" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$19:$B$22,MATCH(4,Calc!$J$19:$J$22,0)),"?")</f>
         <v>Curacao</v>
       </c>
-      <c r="S20" s="145"/>
-      <c r="T20" s="145"/>
-      <c r="U20" s="145"/>
-      <c r="V20" s="145"/>
-      <c r="W20" s="145"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="147"/>
+      <c r="U20" s="147"/>
+      <c r="V20" s="147"/>
+      <c r="W20" s="147"/>
       <c r="X20" s="29">
         <f>IFERROR(INDEX(Calc!$H$19:$H$22,MATCH(4,Calc!$J$19:$J$22,0)),0)</f>
         <v>0</v>
@@ -10032,15 +10029,15 @@
       <c r="AG20" s="28">
         <v>4</v>
       </c>
-      <c r="AH20" s="164" t="str">
+      <c r="AH20" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$23:$B$26,MATCH(4,Calc!$J$23:$J$26,0)),"?")</f>
         <v>Tunisia</v>
       </c>
-      <c r="AI20" s="145"/>
-      <c r="AJ20" s="145"/>
-      <c r="AK20" s="145"/>
-      <c r="AL20" s="145"/>
-      <c r="AM20" s="145"/>
+      <c r="AI20" s="147"/>
+      <c r="AJ20" s="147"/>
+      <c r="AK20" s="147"/>
+      <c r="AL20" s="147"/>
+      <c r="AM20" s="147"/>
       <c r="AN20" s="29">
         <f>IFERROR(INDEX(Calc!$H$23:$H$26,MATCH(4,Calc!$J$23:$J$26,0)),0)</f>
         <v>0</v>
@@ -10078,71 +10075,71 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:48" ht="21.95" customHeight="1">
-      <c r="A22" s="175" t="s">
+    <row r="22" spans="1:48" ht="21.9" customHeight="1">
+      <c r="A22" s="193" t="s">
         <v>172</v>
       </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="145"/>
-      <c r="G22" s="145"/>
-      <c r="H22" s="145"/>
-      <c r="I22" s="145"/>
-      <c r="J22" s="145"/>
-      <c r="K22" s="145"/>
-      <c r="L22" s="145"/>
-      <c r="M22" s="145"/>
-      <c r="N22" s="145"/>
-      <c r="O22" s="145"/>
-      <c r="Q22" s="174" t="s">
+      <c r="B22" s="147"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="147"/>
+      <c r="G22" s="147"/>
+      <c r="H22" s="147"/>
+      <c r="I22" s="147"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="147"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="147"/>
+      <c r="N22" s="147"/>
+      <c r="O22" s="147"/>
+      <c r="Q22" s="197" t="s">
         <v>173</v>
       </c>
-      <c r="R22" s="145"/>
-      <c r="S22" s="145"/>
-      <c r="T22" s="145"/>
-      <c r="U22" s="145"/>
-      <c r="V22" s="145"/>
-      <c r="W22" s="145"/>
-      <c r="X22" s="145"/>
-      <c r="Y22" s="145"/>
-      <c r="Z22" s="145"/>
-      <c r="AA22" s="145"/>
-      <c r="AB22" s="145"/>
-      <c r="AC22" s="145"/>
-      <c r="AD22" s="145"/>
-      <c r="AE22" s="145"/>
-      <c r="AG22" s="169" t="s">
+      <c r="R22" s="147"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="147"/>
+      <c r="U22" s="147"/>
+      <c r="V22" s="147"/>
+      <c r="W22" s="147"/>
+      <c r="X22" s="147"/>
+      <c r="Y22" s="147"/>
+      <c r="Z22" s="147"/>
+      <c r="AA22" s="147"/>
+      <c r="AB22" s="147"/>
+      <c r="AC22" s="147"/>
+      <c r="AD22" s="147"/>
+      <c r="AE22" s="147"/>
+      <c r="AG22" s="203" t="s">
         <v>174</v>
       </c>
-      <c r="AH22" s="145"/>
-      <c r="AI22" s="145"/>
-      <c r="AJ22" s="145"/>
-      <c r="AK22" s="145"/>
-      <c r="AL22" s="145"/>
-      <c r="AM22" s="145"/>
-      <c r="AN22" s="145"/>
-      <c r="AO22" s="145"/>
-      <c r="AP22" s="145"/>
-      <c r="AQ22" s="145"/>
-      <c r="AR22" s="145"/>
-      <c r="AS22" s="145"/>
-      <c r="AT22" s="145"/>
-      <c r="AU22" s="145"/>
+      <c r="AH22" s="147"/>
+      <c r="AI22" s="147"/>
+      <c r="AJ22" s="147"/>
+      <c r="AK22" s="147"/>
+      <c r="AL22" s="147"/>
+      <c r="AM22" s="147"/>
+      <c r="AN22" s="147"/>
+      <c r="AO22" s="147"/>
+      <c r="AP22" s="147"/>
+      <c r="AQ22" s="147"/>
+      <c r="AR22" s="147"/>
+      <c r="AS22" s="147"/>
+      <c r="AT22" s="147"/>
+      <c r="AU22" s="147"/>
     </row>
     <row r="23" spans="1:48" ht="18" customHeight="1">
       <c r="A23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="167" t="s">
+      <c r="B23" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="147"/>
+      <c r="G23" s="147"/>
       <c r="H23" s="21" t="s">
         <v>160</v>
       </c>
@@ -10173,14 +10170,14 @@
       <c r="Q23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R23" s="167" t="s">
+      <c r="R23" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S23" s="145"/>
-      <c r="T23" s="145"/>
-      <c r="U23" s="145"/>
-      <c r="V23" s="145"/>
-      <c r="W23" s="145"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="147"/>
+      <c r="U23" s="147"/>
+      <c r="V23" s="147"/>
+      <c r="W23" s="147"/>
       <c r="X23" s="21" t="s">
         <v>160</v>
       </c>
@@ -10211,14 +10208,14 @@
       <c r="AG23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH23" s="167" t="s">
+      <c r="AH23" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI23" s="145"/>
-      <c r="AJ23" s="145"/>
-      <c r="AK23" s="145"/>
-      <c r="AL23" s="145"/>
-      <c r="AM23" s="145"/>
+      <c r="AI23" s="147"/>
+      <c r="AJ23" s="147"/>
+      <c r="AK23" s="147"/>
+      <c r="AL23" s="147"/>
+      <c r="AM23" s="147"/>
       <c r="AN23" s="21" t="s">
         <v>160</v>
       </c>
@@ -10251,15 +10248,15 @@
       <c r="A24" s="22">
         <v>1</v>
       </c>
-      <c r="B24" s="163" t="str">
+      <c r="B24" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(1,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Belgica</v>
       </c>
-      <c r="C24" s="145"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="145"/>
-      <c r="F24" s="145"/>
-      <c r="G24" s="145"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="147"/>
       <c r="H24" s="23">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(1,Calc!$J$27:$J$30,0)),0)</f>
         <v>9</v>
@@ -10299,15 +10296,15 @@
       <c r="Q24" s="22">
         <v>1</v>
       </c>
-      <c r="R24" s="163" t="str">
+      <c r="R24" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(1,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Espanha</v>
       </c>
-      <c r="S24" s="145"/>
-      <c r="T24" s="145"/>
-      <c r="U24" s="145"/>
-      <c r="V24" s="145"/>
-      <c r="W24" s="145"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="147"/>
+      <c r="U24" s="147"/>
+      <c r="V24" s="147"/>
+      <c r="W24" s="147"/>
       <c r="X24" s="23">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(1,Calc!$J$31:$J$34,0)),0)</f>
         <v>9</v>
@@ -10347,15 +10344,15 @@
       <c r="AG24" s="22">
         <v>1</v>
       </c>
-      <c r="AH24" s="163" t="str">
+      <c r="AH24" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(1,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Franca</v>
       </c>
-      <c r="AI24" s="145"/>
-      <c r="AJ24" s="145"/>
-      <c r="AK24" s="145"/>
-      <c r="AL24" s="145"/>
-      <c r="AM24" s="145"/>
+      <c r="AI24" s="147"/>
+      <c r="AJ24" s="147"/>
+      <c r="AK24" s="147"/>
+      <c r="AL24" s="147"/>
+      <c r="AM24" s="147"/>
       <c r="AN24" s="23">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(1,Calc!$J$35:$J$38,0)),0)</f>
         <v>9</v>
@@ -10397,15 +10394,15 @@
       <c r="A25" s="24">
         <v>2</v>
       </c>
-      <c r="B25" s="152" t="str">
+      <c r="B25" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(2,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Egito</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="145"/>
-      <c r="G25" s="145"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
       <c r="H25" s="25">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(2,Calc!$J$27:$J$30,0)),0)</f>
         <v>4</v>
@@ -10445,15 +10442,15 @@
       <c r="Q25" s="24">
         <v>2</v>
       </c>
-      <c r="R25" s="152" t="str">
+      <c r="R25" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(2,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Uruguai</v>
       </c>
-      <c r="S25" s="145"/>
-      <c r="T25" s="145"/>
-      <c r="U25" s="145"/>
-      <c r="V25" s="145"/>
-      <c r="W25" s="145"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="147"/>
+      <c r="U25" s="147"/>
+      <c r="V25" s="147"/>
+      <c r="W25" s="147"/>
       <c r="X25" s="25">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(2,Calc!$J$31:$J$34,0)),0)</f>
         <v>6</v>
@@ -10493,15 +10490,15 @@
       <c r="AG25" s="24">
         <v>2</v>
       </c>
-      <c r="AH25" s="152" t="str">
+      <c r="AH25" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(2,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Noruega</v>
       </c>
-      <c r="AI25" s="145"/>
-      <c r="AJ25" s="145"/>
-      <c r="AK25" s="145"/>
-      <c r="AL25" s="145"/>
-      <c r="AM25" s="145"/>
+      <c r="AI25" s="147"/>
+      <c r="AJ25" s="147"/>
+      <c r="AK25" s="147"/>
+      <c r="AL25" s="147"/>
+      <c r="AM25" s="147"/>
       <c r="AN25" s="25">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(2,Calc!$J$35:$J$38,0)),0)</f>
         <v>6</v>
@@ -10543,15 +10540,15 @@
       <c r="A26" s="26">
         <v>3</v>
       </c>
-      <c r="B26" s="165" t="str">
+      <c r="B26" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(3,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Ira</v>
       </c>
-      <c r="C26" s="145"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="145"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="145"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="147"/>
+      <c r="G26" s="147"/>
       <c r="H26" s="27">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(3,Calc!$J$27:$J$30,0)),0)</f>
         <v>4</v>
@@ -10591,15 +10588,15 @@
       <c r="Q26" s="26">
         <v>3</v>
       </c>
-      <c r="R26" s="165" t="str">
+      <c r="R26" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(3,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Arabia Saudita</v>
       </c>
-      <c r="S26" s="145"/>
-      <c r="T26" s="145"/>
-      <c r="U26" s="145"/>
-      <c r="V26" s="145"/>
-      <c r="W26" s="145"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="147"/>
+      <c r="U26" s="147"/>
+      <c r="V26" s="147"/>
+      <c r="W26" s="147"/>
       <c r="X26" s="27">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(3,Calc!$J$31:$J$34,0)),0)</f>
         <v>3</v>
@@ -10639,15 +10636,15 @@
       <c r="AG26" s="26">
         <v>3</v>
       </c>
-      <c r="AH26" s="165" t="str">
+      <c r="AH26" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(3,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Senegal</v>
       </c>
-      <c r="AI26" s="145"/>
-      <c r="AJ26" s="145"/>
-      <c r="AK26" s="145"/>
-      <c r="AL26" s="145"/>
-      <c r="AM26" s="145"/>
+      <c r="AI26" s="147"/>
+      <c r="AJ26" s="147"/>
+      <c r="AK26" s="147"/>
+      <c r="AL26" s="147"/>
+      <c r="AM26" s="147"/>
       <c r="AN26" s="27">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(3,Calc!$J$35:$J$38,0)),0)</f>
         <v>3</v>
@@ -10689,15 +10686,15 @@
       <c r="A27" s="28">
         <v>4</v>
       </c>
-      <c r="B27" s="164" t="str">
+      <c r="B27" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$27:$B$30,MATCH(4,Calc!$J$27:$J$30,0)),"?")</f>
         <v>Nova Zelandia</v>
       </c>
-      <c r="C27" s="145"/>
-      <c r="D27" s="145"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="145"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="147"/>
+      <c r="G27" s="147"/>
       <c r="H27" s="29">
         <f>IFERROR(INDEX(Calc!$H$27:$H$30,MATCH(4,Calc!$J$27:$J$30,0)),0)</f>
         <v>0</v>
@@ -10737,15 +10734,15 @@
       <c r="Q27" s="28">
         <v>4</v>
       </c>
-      <c r="R27" s="164" t="str">
+      <c r="R27" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$31:$B$34,MATCH(4,Calc!$J$31:$J$34,0)),"?")</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="S27" s="145"/>
-      <c r="T27" s="145"/>
-      <c r="U27" s="145"/>
-      <c r="V27" s="145"/>
-      <c r="W27" s="145"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="147"/>
+      <c r="U27" s="147"/>
+      <c r="V27" s="147"/>
+      <c r="W27" s="147"/>
       <c r="X27" s="29">
         <f>IFERROR(INDEX(Calc!$H$31:$H$34,MATCH(4,Calc!$J$31:$J$34,0)),0)</f>
         <v>0</v>
@@ -10785,15 +10782,15 @@
       <c r="AG27" s="28">
         <v>4</v>
       </c>
-      <c r="AH27" s="164" t="str">
+      <c r="AH27" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$35:$B$38,MATCH(4,Calc!$J$35:$J$38,0)),"?")</f>
         <v>Iraque</v>
       </c>
-      <c r="AI27" s="145"/>
-      <c r="AJ27" s="145"/>
-      <c r="AK27" s="145"/>
-      <c r="AL27" s="145"/>
-      <c r="AM27" s="145"/>
+      <c r="AI27" s="147"/>
+      <c r="AJ27" s="147"/>
+      <c r="AK27" s="147"/>
+      <c r="AL27" s="147"/>
+      <c r="AM27" s="147"/>
       <c r="AN27" s="29">
         <f>IFERROR(INDEX(Calc!$H$35:$H$38,MATCH(4,Calc!$J$35:$J$38,0)),0)</f>
         <v>0</v>
@@ -10831,71 +10828,71 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:48" ht="21.95" customHeight="1">
-      <c r="A29" s="176" t="s">
+    <row r="29" spans="1:48" ht="21.9" customHeight="1">
+      <c r="A29" s="194" t="s">
         <v>175</v>
       </c>
-      <c r="B29" s="145"/>
-      <c r="C29" s="145"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="145"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="145"/>
-      <c r="H29" s="145"/>
-      <c r="I29" s="145"/>
-      <c r="J29" s="145"/>
-      <c r="K29" s="145"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="145"/>
-      <c r="N29" s="145"/>
-      <c r="O29" s="145"/>
-      <c r="Q29" s="173" t="s">
+      <c r="B29" s="147"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="147"/>
+      <c r="O29" s="147"/>
+      <c r="Q29" s="196" t="s">
         <v>176</v>
       </c>
-      <c r="R29" s="145"/>
-      <c r="S29" s="145"/>
-      <c r="T29" s="145"/>
-      <c r="U29" s="145"/>
-      <c r="V29" s="145"/>
-      <c r="W29" s="145"/>
-      <c r="X29" s="145"/>
-      <c r="Y29" s="145"/>
-      <c r="Z29" s="145"/>
-      <c r="AA29" s="145"/>
-      <c r="AB29" s="145"/>
-      <c r="AC29" s="145"/>
-      <c r="AD29" s="145"/>
-      <c r="AE29" s="145"/>
-      <c r="AG29" s="168" t="s">
+      <c r="R29" s="147"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="147"/>
+      <c r="U29" s="147"/>
+      <c r="V29" s="147"/>
+      <c r="W29" s="147"/>
+      <c r="X29" s="147"/>
+      <c r="Y29" s="147"/>
+      <c r="Z29" s="147"/>
+      <c r="AA29" s="147"/>
+      <c r="AB29" s="147"/>
+      <c r="AC29" s="147"/>
+      <c r="AD29" s="147"/>
+      <c r="AE29" s="147"/>
+      <c r="AG29" s="202" t="s">
         <v>177</v>
       </c>
-      <c r="AH29" s="145"/>
-      <c r="AI29" s="145"/>
-      <c r="AJ29" s="145"/>
-      <c r="AK29" s="145"/>
-      <c r="AL29" s="145"/>
-      <c r="AM29" s="145"/>
-      <c r="AN29" s="145"/>
-      <c r="AO29" s="145"/>
-      <c r="AP29" s="145"/>
-      <c r="AQ29" s="145"/>
-      <c r="AR29" s="145"/>
-      <c r="AS29" s="145"/>
-      <c r="AT29" s="145"/>
-      <c r="AU29" s="145"/>
+      <c r="AH29" s="147"/>
+      <c r="AI29" s="147"/>
+      <c r="AJ29" s="147"/>
+      <c r="AK29" s="147"/>
+      <c r="AL29" s="147"/>
+      <c r="AM29" s="147"/>
+      <c r="AN29" s="147"/>
+      <c r="AO29" s="147"/>
+      <c r="AP29" s="147"/>
+      <c r="AQ29" s="147"/>
+      <c r="AR29" s="147"/>
+      <c r="AS29" s="147"/>
+      <c r="AT29" s="147"/>
+      <c r="AU29" s="147"/>
     </row>
     <row r="30" spans="1:48" ht="18" customHeight="1">
       <c r="A30" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="C30" s="145"/>
-      <c r="D30" s="145"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145"/>
+      <c r="C30" s="147"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="147"/>
       <c r="H30" s="21" t="s">
         <v>160</v>
       </c>
@@ -10926,14 +10923,14 @@
       <c r="Q30" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="R30" s="167" t="s">
+      <c r="R30" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="S30" s="145"/>
-      <c r="T30" s="145"/>
-      <c r="U30" s="145"/>
-      <c r="V30" s="145"/>
-      <c r="W30" s="145"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="147"/>
+      <c r="U30" s="147"/>
+      <c r="V30" s="147"/>
+      <c r="W30" s="147"/>
       <c r="X30" s="21" t="s">
         <v>160</v>
       </c>
@@ -10964,14 +10961,14 @@
       <c r="AG30" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AH30" s="167" t="s">
+      <c r="AH30" s="186" t="s">
         <v>746</v>
       </c>
-      <c r="AI30" s="145"/>
-      <c r="AJ30" s="145"/>
-      <c r="AK30" s="145"/>
-      <c r="AL30" s="145"/>
-      <c r="AM30" s="145"/>
+      <c r="AI30" s="147"/>
+      <c r="AJ30" s="147"/>
+      <c r="AK30" s="147"/>
+      <c r="AL30" s="147"/>
+      <c r="AM30" s="147"/>
       <c r="AN30" s="21" t="s">
         <v>160</v>
       </c>
@@ -11004,15 +11001,15 @@
       <c r="A31" s="22">
         <v>1</v>
       </c>
-      <c r="B31" s="163" t="str">
+      <c r="B31" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(1,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Argentina</v>
       </c>
-      <c r="C31" s="145"/>
-      <c r="D31" s="145"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="145"/>
-      <c r="G31" s="145"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="147"/>
       <c r="H31" s="23">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(1,Calc!$J$39:$J$42,0)),0)</f>
         <v>9</v>
@@ -11052,15 +11049,15 @@
       <c r="Q31" s="22">
         <v>1</v>
       </c>
-      <c r="R31" s="163" t="str">
+      <c r="R31" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(1,Calc!$J$43:$J$46,0)),"?")</f>
         <v>Portugal</v>
       </c>
-      <c r="S31" s="145"/>
-      <c r="T31" s="145"/>
-      <c r="U31" s="145"/>
-      <c r="V31" s="145"/>
-      <c r="W31" s="145"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="147"/>
+      <c r="U31" s="147"/>
+      <c r="V31" s="147"/>
+      <c r="W31" s="147"/>
       <c r="X31" s="23">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(1,Calc!$J$43:$J$46,0)),0)</f>
         <v>7</v>
@@ -11100,15 +11097,15 @@
       <c r="AG31" s="22">
         <v>1</v>
       </c>
-      <c r="AH31" s="163" t="str">
+      <c r="AH31" s="187" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(1,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Inglaterra</v>
       </c>
-      <c r="AI31" s="145"/>
-      <c r="AJ31" s="145"/>
-      <c r="AK31" s="145"/>
-      <c r="AL31" s="145"/>
-      <c r="AM31" s="145"/>
+      <c r="AI31" s="147"/>
+      <c r="AJ31" s="147"/>
+      <c r="AK31" s="147"/>
+      <c r="AL31" s="147"/>
+      <c r="AM31" s="147"/>
       <c r="AN31" s="23">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(1,Calc!$J$47:$J$50,0)),0)</f>
         <v>9</v>
@@ -11150,15 +11147,15 @@
       <c r="A32" s="24">
         <v>2</v>
       </c>
-      <c r="B32" s="152" t="str">
+      <c r="B32" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(2,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Austria</v>
       </c>
-      <c r="C32" s="145"/>
-      <c r="D32" s="145"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="145"/>
+      <c r="C32" s="147"/>
+      <c r="D32" s="147"/>
+      <c r="E32" s="147"/>
+      <c r="F32" s="147"/>
+      <c r="G32" s="147"/>
       <c r="H32" s="25">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(2,Calc!$J$39:$J$42,0)),0)</f>
         <v>4</v>
@@ -11198,15 +11195,15 @@
       <c r="Q32" s="24">
         <v>2</v>
       </c>
-      <c r="R32" s="152" t="str">
+      <c r="R32" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(2,Calc!$J$43:$J$46,0)),"?")</f>
         <v>Colombia</v>
       </c>
-      <c r="S32" s="145"/>
-      <c r="T32" s="145"/>
-      <c r="U32" s="145"/>
-      <c r="V32" s="145"/>
-      <c r="W32" s="145"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="147"/>
+      <c r="U32" s="147"/>
+      <c r="V32" s="147"/>
+      <c r="W32" s="147"/>
       <c r="X32" s="25">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(2,Calc!$J$43:$J$46,0)),0)</f>
         <v>7</v>
@@ -11246,15 +11243,15 @@
       <c r="AG32" s="24">
         <v>2</v>
       </c>
-      <c r="AH32" s="152" t="str">
+      <c r="AH32" s="190" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(2,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Croacia</v>
       </c>
-      <c r="AI32" s="145"/>
-      <c r="AJ32" s="145"/>
-      <c r="AK32" s="145"/>
-      <c r="AL32" s="145"/>
-      <c r="AM32" s="145"/>
+      <c r="AI32" s="147"/>
+      <c r="AJ32" s="147"/>
+      <c r="AK32" s="147"/>
+      <c r="AL32" s="147"/>
+      <c r="AM32" s="147"/>
       <c r="AN32" s="25">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(2,Calc!$J$47:$J$50,0)),0)</f>
         <v>6</v>
@@ -11296,15 +11293,15 @@
       <c r="A33" s="26">
         <v>3</v>
       </c>
-      <c r="B33" s="165" t="str">
+      <c r="B33" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(3,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Argelia</v>
       </c>
-      <c r="C33" s="145"/>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="145"/>
+      <c r="C33" s="147"/>
+      <c r="D33" s="147"/>
+      <c r="E33" s="147"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="147"/>
       <c r="H33" s="27">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(3,Calc!$J$39:$J$42,0)),0)</f>
         <v>4</v>
@@ -11344,15 +11341,15 @@
       <c r="Q33" s="26">
         <v>3</v>
       </c>
-      <c r="R33" s="165" t="str">
+      <c r="R33" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(3,Calc!$J$43:$J$46,0)),"?")</f>
         <v>Uzbequistao</v>
       </c>
-      <c r="S33" s="145"/>
-      <c r="T33" s="145"/>
-      <c r="U33" s="145"/>
-      <c r="V33" s="145"/>
-      <c r="W33" s="145"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="147"/>
+      <c r="U33" s="147"/>
+      <c r="V33" s="147"/>
+      <c r="W33" s="147"/>
       <c r="X33" s="27">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(3,Calc!$J$43:$J$46,0)),0)</f>
         <v>3</v>
@@ -11392,15 +11389,15 @@
       <c r="AG33" s="26">
         <v>3</v>
       </c>
-      <c r="AH33" s="165" t="str">
+      <c r="AH33" s="182" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(3,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Gana</v>
       </c>
-      <c r="AI33" s="145"/>
-      <c r="AJ33" s="145"/>
-      <c r="AK33" s="145"/>
-      <c r="AL33" s="145"/>
-      <c r="AM33" s="145"/>
+      <c r="AI33" s="147"/>
+      <c r="AJ33" s="147"/>
+      <c r="AK33" s="147"/>
+      <c r="AL33" s="147"/>
+      <c r="AM33" s="147"/>
       <c r="AN33" s="27">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(3,Calc!$J$47:$J$50,0)),0)</f>
         <v>3</v>
@@ -11442,15 +11439,15 @@
       <c r="A34" s="28">
         <v>4</v>
       </c>
-      <c r="B34" s="164" t="str">
+      <c r="B34" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$39:$B$42,MATCH(4,Calc!$J$39:$J$42,0)),"?")</f>
         <v>Jordania</v>
       </c>
-      <c r="C34" s="145"/>
-      <c r="D34" s="145"/>
-      <c r="E34" s="145"/>
-      <c r="F34" s="145"/>
-      <c r="G34" s="145"/>
+      <c r="C34" s="147"/>
+      <c r="D34" s="147"/>
+      <c r="E34" s="147"/>
+      <c r="F34" s="147"/>
+      <c r="G34" s="147"/>
       <c r="H34" s="29">
         <f>IFERROR(INDEX(Calc!$H$39:$H$42,MATCH(4,Calc!$J$39:$J$42,0)),0)</f>
         <v>0</v>
@@ -11490,15 +11487,15 @@
       <c r="Q34" s="28">
         <v>4</v>
       </c>
-      <c r="R34" s="164" t="str">
+      <c r="R34" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$43:$B$46,MATCH(4,Calc!$J$43:$J$46,0)),"?")</f>
         <v>RD Congo</v>
       </c>
-      <c r="S34" s="145"/>
-      <c r="T34" s="145"/>
-      <c r="U34" s="145"/>
-      <c r="V34" s="145"/>
-      <c r="W34" s="145"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="147"/>
+      <c r="U34" s="147"/>
+      <c r="V34" s="147"/>
+      <c r="W34" s="147"/>
       <c r="X34" s="29">
         <f>IFERROR(INDEX(Calc!$H$43:$H$46,MATCH(4,Calc!$J$43:$J$46,0)),0)</f>
         <v>0</v>
@@ -11538,15 +11535,15 @@
       <c r="AG34" s="28">
         <v>4</v>
       </c>
-      <c r="AH34" s="164" t="str">
+      <c r="AH34" s="180" t="str">
         <f>IFERROR(INDEX(Calc!$B$47:$B$50,MATCH(4,Calc!$J$47:$J$50,0)),"?")</f>
         <v>Panama</v>
       </c>
-      <c r="AI34" s="145"/>
-      <c r="AJ34" s="145"/>
-      <c r="AK34" s="145"/>
-      <c r="AL34" s="145"/>
-      <c r="AM34" s="145"/>
+      <c r="AI34" s="147"/>
+      <c r="AJ34" s="147"/>
+      <c r="AK34" s="147"/>
+      <c r="AL34" s="147"/>
+      <c r="AM34" s="147"/>
       <c r="AN34" s="29">
         <f>IFERROR(INDEX(Calc!$H$47:$H$50,MATCH(4,Calc!$J$47:$J$50,0)),0)</f>
         <v>0</v>
@@ -11586,6 +11583,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="R18:W18"/>
+    <mergeCell ref="BT3:BU3"/>
+    <mergeCell ref="CF3:CG3"/>
+    <mergeCell ref="AG15:AU15"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="EH3:EI3"/>
+    <mergeCell ref="CR3:CS3"/>
+    <mergeCell ref="DB3:DC3"/>
+    <mergeCell ref="EJ3:EK3"/>
+    <mergeCell ref="CT3:CU3"/>
+    <mergeCell ref="AG8:AU8"/>
+    <mergeCell ref="EF3:EG3"/>
+    <mergeCell ref="EB3:EC3"/>
+    <mergeCell ref="ED3:EE3"/>
+    <mergeCell ref="DD3:DE3"/>
+    <mergeCell ref="BN3:BO3"/>
+    <mergeCell ref="BP3:BQ3"/>
+    <mergeCell ref="DP3:DQ3"/>
+    <mergeCell ref="BZ3:CA3"/>
+    <mergeCell ref="DH3:DI3"/>
+    <mergeCell ref="CB3:CC3"/>
+    <mergeCell ref="DJ3:DK3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="CZ3:DA3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="DR3:DS3"/>
+    <mergeCell ref="R13:W13"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AH20:AM20"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="R12:W12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="CN3:CO3"/>
+    <mergeCell ref="CP3:CQ3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="AZ3:BA3"/>
+    <mergeCell ref="AG29:AU29"/>
+    <mergeCell ref="AH23:AM23"/>
+    <mergeCell ref="CD3:CE3"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="AG22:AU22"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="R26:W26"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A2:EO2"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="BJ3:BK3"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="R10:W10"/>
+    <mergeCell ref="AH24:AM24"/>
+    <mergeCell ref="DL3:DM3"/>
+    <mergeCell ref="R19:W19"/>
+    <mergeCell ref="AH18:AM18"/>
+    <mergeCell ref="BV3:BW3"/>
+    <mergeCell ref="DN3:DO3"/>
+    <mergeCell ref="BX3:BY3"/>
+    <mergeCell ref="DF3:DG3"/>
+    <mergeCell ref="DX3:DY3"/>
+    <mergeCell ref="DZ3:EA3"/>
+    <mergeCell ref="AH17:AM17"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="AH11:AM11"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="R23:W23"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="R34:W34"/>
+    <mergeCell ref="R16:W16"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="CH3:CI3"/>
+    <mergeCell ref="BB3:BC3"/>
+    <mergeCell ref="CJ3:CK3"/>
+    <mergeCell ref="CL3:CM3"/>
+    <mergeCell ref="R27:W27"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="R24:W24"/>
+    <mergeCell ref="R33:W33"/>
+    <mergeCell ref="AH33:AM33"/>
+    <mergeCell ref="R30:W30"/>
+    <mergeCell ref="R25:W25"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="AH19:AM19"/>
+    <mergeCell ref="AH26:AM26"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="AH34:AM34"/>
+    <mergeCell ref="AH27:AM27"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="R31:W31"/>
+    <mergeCell ref="R32:W32"/>
+    <mergeCell ref="AH30:AM30"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AH32:AM32"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="AH31:AM31"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AH16:AM16"/>
+    <mergeCell ref="AH25:AM25"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="EL3:EM3"/>
     <mergeCell ref="CV3:CW3"/>
     <mergeCell ref="EN3:EO3"/>
@@ -11610,129 +11730,6 @@
     <mergeCell ref="R11:W11"/>
     <mergeCell ref="AR3:AS3"/>
     <mergeCell ref="AB3:AC3"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="AH34:AM34"/>
-    <mergeCell ref="AH27:AM27"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="R31:W31"/>
-    <mergeCell ref="R32:W32"/>
-    <mergeCell ref="AH30:AM30"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AH32:AM32"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="AH31:AM31"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="AH25:AM25"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="R34:W34"/>
-    <mergeCell ref="R16:W16"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="CH3:CI3"/>
-    <mergeCell ref="BB3:BC3"/>
-    <mergeCell ref="CJ3:CK3"/>
-    <mergeCell ref="CL3:CM3"/>
-    <mergeCell ref="R27:W27"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="R24:W24"/>
-    <mergeCell ref="R33:W33"/>
-    <mergeCell ref="AH33:AM33"/>
-    <mergeCell ref="R30:W30"/>
-    <mergeCell ref="R25:W25"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="AH19:AM19"/>
-    <mergeCell ref="AH26:AM26"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="A2:EO2"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="BJ3:BK3"/>
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="R10:W10"/>
-    <mergeCell ref="AH24:AM24"/>
-    <mergeCell ref="DL3:DM3"/>
-    <mergeCell ref="R19:W19"/>
-    <mergeCell ref="AH18:AM18"/>
-    <mergeCell ref="BV3:BW3"/>
-    <mergeCell ref="DN3:DO3"/>
-    <mergeCell ref="BX3:BY3"/>
-    <mergeCell ref="DF3:DG3"/>
-    <mergeCell ref="DX3:DY3"/>
-    <mergeCell ref="DZ3:EA3"/>
-    <mergeCell ref="AH17:AM17"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="R23:W23"/>
-    <mergeCell ref="AH13:AM13"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="DR3:DS3"/>
-    <mergeCell ref="R13:W13"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AH20:AM20"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="R12:W12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="CN3:CO3"/>
-    <mergeCell ref="CP3:CQ3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="AZ3:BA3"/>
-    <mergeCell ref="AG29:AU29"/>
-    <mergeCell ref="AH23:AM23"/>
-    <mergeCell ref="CD3:CE3"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="AG22:AU22"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="R26:W26"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="EH3:EI3"/>
-    <mergeCell ref="CR3:CS3"/>
-    <mergeCell ref="DB3:DC3"/>
-    <mergeCell ref="EJ3:EK3"/>
-    <mergeCell ref="CT3:CU3"/>
-    <mergeCell ref="AG8:AU8"/>
-    <mergeCell ref="EF3:EG3"/>
-    <mergeCell ref="EB3:EC3"/>
-    <mergeCell ref="ED3:EE3"/>
-    <mergeCell ref="DD3:DE3"/>
-    <mergeCell ref="BN3:BO3"/>
-    <mergeCell ref="BP3:BQ3"/>
-    <mergeCell ref="DP3:DQ3"/>
-    <mergeCell ref="BZ3:CA3"/>
-    <mergeCell ref="DH3:DI3"/>
-    <mergeCell ref="CB3:CC3"/>
-    <mergeCell ref="DJ3:DK3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="CZ3:DA3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="R18:W18"/>
-    <mergeCell ref="BT3:BU3"/>
-    <mergeCell ref="CF3:CG3"/>
-    <mergeCell ref="AG15:AU15"/>
-    <mergeCell ref="A15:O15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11741,11 +11738,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF50B69-7C30-4E8D-8A33-5820F111502A}">
   <dimension ref="A1:D817"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -18445,7 +18442,7 @@
     <tabColor rgb="FF607D8B"/>
   </sheetPr>
   <dimension ref="A1:M88"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -18455,20 +18452,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="35" t="s">
@@ -21469,27 +21466,27 @@
     <tabColor rgb="FF607D8B"/>
   </sheetPr>
   <dimension ref="A1:J497"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-    </row>
-    <row r="2" spans="1:10" ht="21.95" customHeight="1">
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+    </row>
+    <row r="2" spans="1:10" ht="21.9" customHeight="1">
       <c r="A2" s="114" t="s">
         <v>193</v>
       </c>
@@ -35887,28 +35884,28 @@
     <tabColor rgb="FFE67E22"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="44.1" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>1595</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
     </row>
     <row r="2" spans="1:3" ht="27" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="172" t="s">
         <v>1597</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-    </row>
-    <row r="3" spans="1:3" ht="27.95" customHeight="1">
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+    </row>
+    <row r="3" spans="1:3" ht="27.9" customHeight="1">
       <c r="A3" s="30" t="s">
         <v>34</v>
       </c>
@@ -35919,20 +35916,20 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="27.95" customHeight="1">
+    <row r="4" spans="1:3" ht="27.9" customHeight="1">
       <c r="A4" s="32" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
     </row>
-    <row r="5" spans="1:3" ht="27.95" customHeight="1">
+    <row r="5" spans="1:3" ht="27.9" customHeight="1">
       <c r="A5" s="34" t="str">
         <f>'Apostas - Grupos'!A5</f>
         <v>Renata Mello</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>1616</v>
+        <v>1424</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>136</v>
@@ -35971,427 +35968,427 @@
     <tabColor rgb="FF922B21"/>
   </sheetPr>
   <dimension ref="A1:BM6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="65" width="13.140625" customWidth="1"/>
+    <col min="2" max="65" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:65" ht="44.1" customHeight="1" thickBot="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="158" t="s">
         <v>1591</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="145"/>
-      <c r="X1" s="145"/>
-      <c r="Y1" s="145"/>
-      <c r="Z1" s="145"/>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="145"/>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="145"/>
-      <c r="AG1" s="145"/>
-      <c r="AH1" s="145"/>
-      <c r="AI1" s="145"/>
-      <c r="AJ1" s="145"/>
-      <c r="AK1" s="145"/>
-      <c r="AL1" s="145"/>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="145"/>
-      <c r="AO1" s="145"/>
-      <c r="AP1" s="145"/>
-      <c r="AQ1" s="145"/>
-      <c r="AR1" s="145"/>
-      <c r="AS1" s="145"/>
-      <c r="AT1" s="145"/>
-      <c r="AU1" s="145"/>
-      <c r="AV1" s="145"/>
-      <c r="AW1" s="145"/>
-      <c r="AX1" s="145"/>
-      <c r="AY1" s="145"/>
-      <c r="AZ1" s="145"/>
-      <c r="BA1" s="145"/>
-      <c r="BB1" s="145"/>
-      <c r="BC1" s="145"/>
-      <c r="BD1" s="145"/>
-      <c r="BE1" s="145"/>
-      <c r="BF1" s="145"/>
-      <c r="BG1" s="145"/>
-      <c r="BH1" s="145"/>
-      <c r="BI1" s="145"/>
-      <c r="BJ1" s="145"/>
-      <c r="BK1" s="145"/>
-      <c r="BL1" s="145"/>
-      <c r="BM1" s="145"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="147"/>
+      <c r="AC1" s="147"/>
+      <c r="AD1" s="147"/>
+      <c r="AE1" s="147"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="147"/>
+      <c r="AH1" s="147"/>
+      <c r="AI1" s="147"/>
+      <c r="AJ1" s="147"/>
+      <c r="AK1" s="147"/>
+      <c r="AL1" s="147"/>
+      <c r="AM1" s="147"/>
+      <c r="AN1" s="147"/>
+      <c r="AO1" s="147"/>
+      <c r="AP1" s="147"/>
+      <c r="AQ1" s="147"/>
+      <c r="AR1" s="147"/>
+      <c r="AS1" s="147"/>
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="147"/>
+      <c r="AV1" s="147"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="147"/>
+      <c r="BA1" s="147"/>
+      <c r="BB1" s="147"/>
+      <c r="BC1" s="147"/>
+      <c r="BD1" s="147"/>
+      <c r="BE1" s="147"/>
+      <c r="BF1" s="147"/>
+      <c r="BG1" s="147"/>
+      <c r="BH1" s="147"/>
+      <c r="BI1" s="147"/>
+      <c r="BJ1" s="147"/>
+      <c r="BK1" s="147"/>
+      <c r="BL1" s="147"/>
+      <c r="BM1" s="147"/>
     </row>
     <row r="2" spans="1:65" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="172" t="s">
         <v>1599</v>
       </c>
-      <c r="B2" s="170"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
-      <c r="O2" s="170"/>
-      <c r="P2" s="170"/>
-      <c r="Q2" s="170"/>
-      <c r="R2" s="170"/>
-      <c r="S2" s="170"/>
-      <c r="T2" s="170"/>
-      <c r="U2" s="170"/>
-      <c r="V2" s="170"/>
-      <c r="W2" s="170"/>
-      <c r="X2" s="170"/>
-      <c r="Y2" s="170"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="170"/>
-      <c r="AB2" s="170"/>
-      <c r="AC2" s="170"/>
-      <c r="AD2" s="170"/>
-      <c r="AE2" s="170"/>
-      <c r="AF2" s="170"/>
-      <c r="AG2" s="187"/>
-      <c r="AH2" s="184" t="s">
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="172"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="172"/>
+      <c r="U2" s="172"/>
+      <c r="V2" s="172"/>
+      <c r="W2" s="172"/>
+      <c r="X2" s="172"/>
+      <c r="Y2" s="172"/>
+      <c r="Z2" s="172"/>
+      <c r="AA2" s="172"/>
+      <c r="AB2" s="172"/>
+      <c r="AC2" s="172"/>
+      <c r="AD2" s="172"/>
+      <c r="AE2" s="172"/>
+      <c r="AF2" s="172"/>
+      <c r="AG2" s="173"/>
+      <c r="AH2" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="AI2" s="185"/>
-      <c r="AJ2" s="185"/>
-      <c r="AK2" s="185"/>
-      <c r="AL2" s="185"/>
-      <c r="AM2" s="185"/>
-      <c r="AN2" s="185"/>
-      <c r="AO2" s="185"/>
-      <c r="AP2" s="185"/>
-      <c r="AQ2" s="185"/>
-      <c r="AR2" s="185"/>
-      <c r="AS2" s="185"/>
-      <c r="AT2" s="185"/>
-      <c r="AU2" s="185"/>
-      <c r="AV2" s="185"/>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="184" t="s">
+      <c r="AI2" s="170"/>
+      <c r="AJ2" s="170"/>
+      <c r="AK2" s="170"/>
+      <c r="AL2" s="170"/>
+      <c r="AM2" s="170"/>
+      <c r="AN2" s="170"/>
+      <c r="AO2" s="170"/>
+      <c r="AP2" s="170"/>
+      <c r="AQ2" s="170"/>
+      <c r="AR2" s="170"/>
+      <c r="AS2" s="170"/>
+      <c r="AT2" s="170"/>
+      <c r="AU2" s="170"/>
+      <c r="AV2" s="170"/>
+      <c r="AW2" s="171"/>
+      <c r="AX2" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="AY2" s="185"/>
-      <c r="AZ2" s="185"/>
-      <c r="BA2" s="185"/>
-      <c r="BB2" s="185"/>
-      <c r="BC2" s="185"/>
-      <c r="BD2" s="185"/>
-      <c r="BE2" s="186"/>
-      <c r="BF2" s="184" t="s">
+      <c r="AY2" s="170"/>
+      <c r="AZ2" s="170"/>
+      <c r="BA2" s="170"/>
+      <c r="BB2" s="170"/>
+      <c r="BC2" s="170"/>
+      <c r="BD2" s="170"/>
+      <c r="BE2" s="171"/>
+      <c r="BF2" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="BG2" s="185"/>
-      <c r="BH2" s="185"/>
-      <c r="BI2" s="186"/>
-      <c r="BJ2" s="180" t="s">
+      <c r="BG2" s="170"/>
+      <c r="BH2" s="170"/>
+      <c r="BI2" s="171"/>
+      <c r="BJ2" s="165" t="s">
         <v>1614</v>
       </c>
-      <c r="BK2" s="181"/>
-      <c r="BL2" s="182" t="s">
+      <c r="BK2" s="166"/>
+      <c r="BL2" s="167" t="s">
         <v>1613</v>
       </c>
-      <c r="BM2" s="183"/>
-    </row>
-    <row r="3" spans="1:65" ht="21.95" customHeight="1">
+      <c r="BM2" s="168"/>
+    </row>
+    <row r="3" spans="1:65" ht="21.9" customHeight="1">
       <c r="A3" s="119" t="s">
         <v>709</v>
       </c>
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="151" t="s">
         <v>710</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="189" t="s">
+      <c r="C3" s="147"/>
+      <c r="D3" s="151" t="s">
         <v>711</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="189" t="s">
+      <c r="E3" s="147"/>
+      <c r="F3" s="151" t="s">
         <v>712</v>
       </c>
-      <c r="G3" s="145"/>
-      <c r="H3" s="189" t="s">
+      <c r="G3" s="147"/>
+      <c r="H3" s="151" t="s">
         <v>713</v>
       </c>
-      <c r="I3" s="145"/>
-      <c r="J3" s="189" t="s">
+      <c r="I3" s="147"/>
+      <c r="J3" s="151" t="s">
         <v>714</v>
       </c>
-      <c r="K3" s="145"/>
-      <c r="L3" s="189" t="s">
+      <c r="K3" s="147"/>
+      <c r="L3" s="151" t="s">
         <v>715</v>
       </c>
-      <c r="M3" s="145"/>
-      <c r="N3" s="189" t="s">
+      <c r="M3" s="147"/>
+      <c r="N3" s="151" t="s">
         <v>716</v>
       </c>
-      <c r="O3" s="145"/>
-      <c r="P3" s="189" t="s">
+      <c r="O3" s="147"/>
+      <c r="P3" s="151" t="s">
         <v>717</v>
       </c>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="189" t="s">
+      <c r="Q3" s="147"/>
+      <c r="R3" s="151" t="s">
         <v>718</v>
       </c>
-      <c r="S3" s="145"/>
-      <c r="T3" s="189" t="s">
+      <c r="S3" s="147"/>
+      <c r="T3" s="151" t="s">
         <v>719</v>
       </c>
-      <c r="U3" s="145"/>
-      <c r="V3" s="189" t="s">
+      <c r="U3" s="147"/>
+      <c r="V3" s="151" t="s">
         <v>720</v>
       </c>
-      <c r="W3" s="145"/>
-      <c r="X3" s="189" t="s">
+      <c r="W3" s="147"/>
+      <c r="X3" s="151" t="s">
         <v>721</v>
       </c>
-      <c r="Y3" s="145"/>
-      <c r="Z3" s="189" t="s">
+      <c r="Y3" s="147"/>
+      <c r="Z3" s="151" t="s">
         <v>722</v>
       </c>
-      <c r="AA3" s="145"/>
-      <c r="AB3" s="189" t="s">
+      <c r="AA3" s="147"/>
+      <c r="AB3" s="151" t="s">
         <v>723</v>
       </c>
-      <c r="AC3" s="145"/>
-      <c r="AD3" s="189" t="s">
+      <c r="AC3" s="147"/>
+      <c r="AD3" s="151" t="s">
         <v>724</v>
       </c>
-      <c r="AE3" s="145"/>
-      <c r="AF3" s="189" t="s">
+      <c r="AE3" s="147"/>
+      <c r="AF3" s="151" t="s">
         <v>725</v>
       </c>
-      <c r="AG3" s="145"/>
-      <c r="AH3" s="191" t="s">
+      <c r="AG3" s="147"/>
+      <c r="AH3" s="163" t="s">
         <v>726</v>
       </c>
-      <c r="AI3" s="145"/>
-      <c r="AJ3" s="192" t="s">
+      <c r="AI3" s="147"/>
+      <c r="AJ3" s="156" t="s">
         <v>727</v>
       </c>
-      <c r="AK3" s="145"/>
-      <c r="AL3" s="192" t="s">
+      <c r="AK3" s="147"/>
+      <c r="AL3" s="156" t="s">
         <v>728</v>
       </c>
-      <c r="AM3" s="145"/>
-      <c r="AN3" s="192" t="s">
+      <c r="AM3" s="147"/>
+      <c r="AN3" s="156" t="s">
         <v>729</v>
       </c>
-      <c r="AO3" s="145"/>
-      <c r="AP3" s="192" t="s">
+      <c r="AO3" s="147"/>
+      <c r="AP3" s="156" t="s">
         <v>730</v>
       </c>
-      <c r="AQ3" s="145"/>
-      <c r="AR3" s="192" t="s">
+      <c r="AQ3" s="147"/>
+      <c r="AR3" s="156" t="s">
         <v>731</v>
       </c>
-      <c r="AS3" s="145"/>
-      <c r="AT3" s="192" t="s">
+      <c r="AS3" s="147"/>
+      <c r="AT3" s="156" t="s">
         <v>732</v>
       </c>
-      <c r="AU3" s="145"/>
-      <c r="AV3" s="192" t="s">
+      <c r="AU3" s="147"/>
+      <c r="AV3" s="156" t="s">
         <v>733</v>
       </c>
-      <c r="AW3" s="194"/>
-      <c r="AX3" s="195" t="s">
+      <c r="AW3" s="145"/>
+      <c r="AX3" s="164" t="s">
         <v>734</v>
       </c>
-      <c r="AY3" s="145"/>
-      <c r="AZ3" s="196" t="s">
+      <c r="AY3" s="147"/>
+      <c r="AZ3" s="153" t="s">
         <v>735</v>
       </c>
-      <c r="BA3" s="145"/>
-      <c r="BB3" s="196" t="s">
+      <c r="BA3" s="147"/>
+      <c r="BB3" s="153" t="s">
         <v>736</v>
       </c>
-      <c r="BC3" s="145"/>
-      <c r="BD3" s="196" t="s">
+      <c r="BC3" s="147"/>
+      <c r="BD3" s="153" t="s">
         <v>737</v>
       </c>
-      <c r="BE3" s="194"/>
-      <c r="BF3" s="205" t="s">
+      <c r="BE3" s="145"/>
+      <c r="BF3" s="148" t="s">
         <v>738</v>
       </c>
-      <c r="BG3" s="145"/>
-      <c r="BH3" s="206" t="s">
+      <c r="BG3" s="147"/>
+      <c r="BH3" s="149" t="s">
         <v>739</v>
       </c>
-      <c r="BI3" s="194"/>
-      <c r="BJ3" s="200" t="s">
+      <c r="BI3" s="145"/>
+      <c r="BJ3" s="152" t="s">
         <v>740</v>
       </c>
-      <c r="BK3" s="194"/>
-      <c r="BL3" s="204" t="s">
+      <c r="BK3" s="145"/>
+      <c r="BL3" s="144" t="s">
         <v>741</v>
       </c>
-      <c r="BM3" s="194"/>
-    </row>
-    <row r="4" spans="1:65" ht="15.95" customHeight="1">
+      <c r="BM3" s="145"/>
+    </row>
+    <row r="4" spans="1:65" ht="15.9" customHeight="1">
       <c r="A4" s="120" t="s">
         <v>742</v>
       </c>
-      <c r="B4" s="188">
+      <c r="B4" s="150">
         <v>46201</v>
       </c>
-      <c r="C4" s="145"/>
-      <c r="D4" s="188">
+      <c r="C4" s="147"/>
+      <c r="D4" s="150">
         <v>46202</v>
       </c>
-      <c r="E4" s="145"/>
-      <c r="F4" s="188">
+      <c r="E4" s="147"/>
+      <c r="F4" s="150">
         <v>46202</v>
       </c>
-      <c r="G4" s="145"/>
-      <c r="H4" s="188">
+      <c r="G4" s="147"/>
+      <c r="H4" s="150">
         <v>46202</v>
       </c>
-      <c r="I4" s="145"/>
-      <c r="J4" s="188">
+      <c r="I4" s="147"/>
+      <c r="J4" s="150">
         <v>46203</v>
       </c>
-      <c r="K4" s="145"/>
-      <c r="L4" s="188">
+      <c r="K4" s="147"/>
+      <c r="L4" s="150">
         <v>46203</v>
       </c>
-      <c r="M4" s="145"/>
-      <c r="N4" s="188">
+      <c r="M4" s="147"/>
+      <c r="N4" s="150">
         <v>46203</v>
       </c>
-      <c r="O4" s="145"/>
-      <c r="P4" s="188">
+      <c r="O4" s="147"/>
+      <c r="P4" s="150">
         <v>46204</v>
       </c>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="188">
+      <c r="Q4" s="147"/>
+      <c r="R4" s="150">
         <v>46204</v>
       </c>
-      <c r="S4" s="145"/>
-      <c r="T4" s="188">
+      <c r="S4" s="147"/>
+      <c r="T4" s="150">
         <v>46204</v>
       </c>
-      <c r="U4" s="145"/>
-      <c r="V4" s="188">
+      <c r="U4" s="147"/>
+      <c r="V4" s="150">
         <v>46205</v>
       </c>
-      <c r="W4" s="145"/>
-      <c r="X4" s="188">
+      <c r="W4" s="147"/>
+      <c r="X4" s="150">
         <v>46205</v>
       </c>
-      <c r="Y4" s="145"/>
-      <c r="Z4" s="188">
+      <c r="Y4" s="147"/>
+      <c r="Z4" s="150">
         <v>46205</v>
       </c>
-      <c r="AA4" s="145"/>
-      <c r="AB4" s="188">
+      <c r="AA4" s="147"/>
+      <c r="AB4" s="150">
         <v>46206</v>
       </c>
-      <c r="AC4" s="145"/>
-      <c r="AD4" s="188">
+      <c r="AC4" s="147"/>
+      <c r="AD4" s="150">
         <v>46206</v>
       </c>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="188">
+      <c r="AE4" s="147"/>
+      <c r="AF4" s="150">
         <v>46206</v>
       </c>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="202">
+      <c r="AG4" s="147"/>
+      <c r="AH4" s="155">
         <v>46207</v>
       </c>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="193">
+      <c r="AI4" s="147"/>
+      <c r="AJ4" s="146">
         <v>46207</v>
       </c>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="193">
+      <c r="AK4" s="147"/>
+      <c r="AL4" s="146">
         <v>46208</v>
       </c>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="193">
+      <c r="AM4" s="147"/>
+      <c r="AN4" s="146">
         <v>46208</v>
       </c>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="193">
+      <c r="AO4" s="147"/>
+      <c r="AP4" s="146">
         <v>46209</v>
       </c>
-      <c r="AQ4" s="145"/>
-      <c r="AR4" s="193">
+      <c r="AQ4" s="147"/>
+      <c r="AR4" s="146">
         <v>46209</v>
       </c>
-      <c r="AS4" s="145"/>
-      <c r="AT4" s="193">
+      <c r="AS4" s="147"/>
+      <c r="AT4" s="146">
         <v>46210</v>
       </c>
-      <c r="AU4" s="145"/>
-      <c r="AV4" s="193">
+      <c r="AU4" s="147"/>
+      <c r="AV4" s="146">
         <v>46210</v>
       </c>
-      <c r="AW4" s="194"/>
-      <c r="AX4" s="190">
+      <c r="AW4" s="145"/>
+      <c r="AX4" s="162">
         <v>46212</v>
       </c>
-      <c r="AY4" s="145"/>
-      <c r="AZ4" s="197">
+      <c r="AY4" s="147"/>
+      <c r="AZ4" s="159">
         <v>46213</v>
       </c>
-      <c r="BA4" s="145"/>
-      <c r="BB4" s="197">
+      <c r="BA4" s="147"/>
+      <c r="BB4" s="159">
         <v>46214</v>
       </c>
-      <c r="BC4" s="145"/>
-      <c r="BD4" s="197">
+      <c r="BC4" s="147"/>
+      <c r="BD4" s="159">
         <v>46214</v>
       </c>
-      <c r="BE4" s="194"/>
-      <c r="BF4" s="198">
+      <c r="BE4" s="145"/>
+      <c r="BF4" s="160">
         <v>46217</v>
       </c>
-      <c r="BG4" s="145"/>
-      <c r="BH4" s="201">
+      <c r="BG4" s="147"/>
+      <c r="BH4" s="154">
         <v>46218</v>
       </c>
-      <c r="BI4" s="194"/>
-      <c r="BJ4" s="203">
+      <c r="BI4" s="145"/>
+      <c r="BJ4" s="157">
         <v>46221</v>
       </c>
-      <c r="BK4" s="194"/>
-      <c r="BL4" s="199">
+      <c r="BK4" s="145"/>
+      <c r="BL4" s="161">
         <v>46222</v>
       </c>
-      <c r="BM4" s="194"/>
-    </row>
-    <row r="5" spans="1:65" ht="21.95" customHeight="1">
+      <c r="BM4" s="145"/>
+    </row>
+    <row r="5" spans="1:65" ht="21.9" customHeight="1">
       <c r="A5" s="34" t="str">
         <f>'Apostas - Grupos'!A5</f>
         <v>Renata Mello</v>
@@ -36659,140 +36656,185 @@
       </c>
       <c r="B6" s="123"/>
       <c r="C6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E6" s="123"/>
       <c r="F6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="G6" s="123"/>
       <c r="H6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="I6" s="123"/>
       <c r="J6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="K6" s="123"/>
       <c r="L6" s="123"/>
       <c r="M6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="N6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="O6" s="123"/>
       <c r="P6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="Q6" s="123"/>
       <c r="R6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="S6" s="123"/>
       <c r="T6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="U6" s="123"/>
       <c r="V6" s="123"/>
       <c r="W6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="X6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="Y6" s="123"/>
       <c r="Z6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AA6" s="123"/>
       <c r="AB6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AC6" s="123"/>
       <c r="AD6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AE6" s="123"/>
       <c r="AF6" s="123" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AG6" s="138"/>
       <c r="AH6" s="141"/>
       <c r="AI6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AJ6" s="142"/>
       <c r="AK6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AL6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AM6" s="142"/>
       <c r="AN6" s="142"/>
       <c r="AO6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AP6" s="142"/>
       <c r="AQ6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AR6" s="142"/>
       <c r="AS6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AT6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AU6" s="142"/>
       <c r="AV6" s="142"/>
       <c r="AW6" s="143" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AX6" s="141" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="AY6" s="142"/>
       <c r="AZ6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BA6" s="142"/>
       <c r="BB6" s="142"/>
       <c r="BC6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BD6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BE6" s="143"/>
       <c r="BF6" s="141"/>
       <c r="BG6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BH6" s="142" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BI6" s="143"/>
       <c r="BJ6" s="141" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BK6" s="143"/>
       <c r="BL6" s="141" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="BM6" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="71">
-    <mergeCell ref="BL3:BM3"/>
-    <mergeCell ref="AJ4:AK4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="BF3:BG3"/>
-    <mergeCell ref="BH3:BI3"/>
+    <mergeCell ref="BJ2:BK2"/>
+    <mergeCell ref="BL2:BM2"/>
+    <mergeCell ref="BF2:BI2"/>
+    <mergeCell ref="AH2:AW2"/>
+    <mergeCell ref="A2:AG2"/>
+    <mergeCell ref="AX2:BE2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="AR4:AS4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="AX3:AY3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="AR3:AS3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AT3:AU3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="AV3:AW3"/>
+    <mergeCell ref="AD3:AE3"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="A1:BM1"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BL4:BM4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="AB3:AC3"/>
@@ -36809,56 +36851,11 @@
     <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="BB3:BC3"/>
     <mergeCell ref="BJ4:BK4"/>
-    <mergeCell ref="A1:BM1"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BL4:BM4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AT3:AU3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="AV3:AW3"/>
-    <mergeCell ref="AD3:AE3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AR4:AS4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="AX3:AY3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="AR3:AS3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="BJ2:BK2"/>
-    <mergeCell ref="BL2:BM2"/>
-    <mergeCell ref="BF2:BI2"/>
-    <mergeCell ref="AH2:AW2"/>
-    <mergeCell ref="A2:AG2"/>
-    <mergeCell ref="AX2:BE2"/>
+    <mergeCell ref="BL3:BM3"/>
+    <mergeCell ref="AJ4:AK4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="BF3:BG3"/>
+    <mergeCell ref="BH3:BI3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
